--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/制造_职业配置表_Manufacture_ClassConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/制造_职业配置表_Manufacture_ClassConfig.xlsx
@@ -172,7 +172,7 @@
     <t>1</t>
   </si>
   <si>
-    <t>App_90</t>
+    <t>App_02</t>
   </si>
   <si>
     <t>Class_Archer</t>
@@ -193,7 +193,7 @@
     <t>6</t>
   </si>
   <si>
-    <t>App_91</t>
+    <t>App_03</t>
   </si>
   <si>
     <t>Class_Mage</t>
@@ -223,7 +223,7 @@
     <t>骑士</t>
   </si>
   <si>
-    <t>App_93</t>
+    <t>App_05</t>
   </si>
   <si>
     <t>Class_Rogue</t>
@@ -238,7 +238,7 @@
     <t>5</t>
   </si>
   <si>
-    <t>App_94</t>
+    <t>App_07</t>
   </si>
   <si>
     <t>Class_Priest</t>
@@ -256,7 +256,7 @@
     <t>10</t>
   </si>
   <si>
-    <t>App_95</t>
+    <t>App_09</t>
   </si>
   <si>
     <t>Class_Berserker</t>
@@ -268,7 +268,7 @@
     <t>4</t>
   </si>
   <si>
-    <t>App_96</t>
+    <t>App_04</t>
   </si>
   <si>
     <t>Class_Ranger</t>
@@ -286,9 +286,6 @@
     <t>7</t>
   </si>
   <si>
-    <t>App_97</t>
-  </si>
-  <si>
     <t>Class_Warlock</t>
   </si>
   <si>
@@ -304,7 +301,7 @@
     <t>9</t>
   </si>
   <si>
-    <t>App_98</t>
+    <t>App_08</t>
   </si>
   <si>
     <t>Class_Paladin</t>
@@ -314,6 +311,9 @@
   </si>
   <si>
     <t>1.5</t>
+  </si>
+  <si>
+    <t>App_06</t>
   </si>
   <si>
     <t>Class_Servants</t>
@@ -341,7 +341,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -351,13 +351,6 @@
     </font>
     <font>
       <sz val="12"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -811,153 +804,154 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1532,7 +1526,7 @@
       <c r="K6" t="s">
         <v>59</v>
       </c>
-      <c r="L6" s="1" t="s">
+      <c r="L6" s="2" t="s">
         <v>60</v>
       </c>
     </row>
@@ -1723,15 +1717,15 @@
         <v>83</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>84</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" ht="14.25" spans="1:12">
       <c r="A12" t="s">
+        <v>84</v>
+      </c>
+      <c r="B12" t="s">
         <v>85</v>
-      </c>
-      <c r="B12" t="s">
-        <v>86</v>
       </c>
       <c r="C12" t="s">
         <v>56</v>
@@ -1740,13 +1734,13 @@
         <v>39</v>
       </c>
       <c r="E12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F12" t="s">
         <v>41</v>
       </c>
       <c r="G12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H12" t="s">
         <v>45</v>
@@ -1758,18 +1752,18 @@
         <v>51</v>
       </c>
       <c r="K12" t="s">
+        <v>88</v>
+      </c>
+      <c r="L12" s="1" t="s">
         <v>89</v>
-      </c>
-      <c r="L12" s="1" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="13" ht="14.25" spans="1:12">
       <c r="A13" t="s">
+        <v>90</v>
+      </c>
+      <c r="B13" t="s">
         <v>91</v>
-      </c>
-      <c r="B13" t="s">
-        <v>92</v>
       </c>
       <c r="C13" t="s">
         <v>38</v>
@@ -1790,7 +1784,7 @@
         <v>42</v>
       </c>
       <c r="I13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J13" t="s">
         <v>44</v>
@@ -1799,7 +1793,7 @@
         <v>66</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14" spans="1:12">

--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/制造_职业配置表_Manufacture_ClassConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/制造_职业配置表_Manufacture_ClassConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="120">
   <si>
     <t>职业ID</t>
   </si>
@@ -172,7 +172,7 @@
     <t>1</t>
   </si>
   <si>
-    <t>App_02</t>
+    <t>App_0_01</t>
   </si>
   <si>
     <t>Class_Archer</t>
@@ -190,102 +190,177 @@
     <t>Ranged</t>
   </si>
   <si>
-    <t>6</t>
+    <t>App_0_11</t>
+  </si>
+  <si>
+    <t>Class_Mage</t>
+  </si>
+  <si>
+    <t>法师</t>
+  </si>
+  <si>
+    <t>Intelligence</t>
+  </si>
+  <si>
+    <t>0.8</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>App_0_21</t>
+  </si>
+  <si>
+    <t>Class_Rogue</t>
+  </si>
+  <si>
+    <t>盗贼</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>App_0_31</t>
+  </si>
+  <si>
+    <t>Class_Guardian</t>
+  </si>
+  <si>
+    <t>近卫</t>
+  </si>
+  <si>
+    <t>App_0_02</t>
+  </si>
+  <si>
+    <t>Class_BombMaster</t>
+  </si>
+  <si>
+    <t>炸弹师</t>
+  </si>
+  <si>
+    <t>App_0_12</t>
+  </si>
+  <si>
+    <t>Class_IceMage</t>
+  </si>
+  <si>
+    <t>冰法</t>
+  </si>
+  <si>
+    <t>App_0_22</t>
+  </si>
+  <si>
+    <t>Class_Brawler</t>
+  </si>
+  <si>
+    <t>格斗师</t>
+  </si>
+  <si>
+    <t>App_0_32</t>
+  </si>
+  <si>
+    <t>Class_Berserker</t>
+  </si>
+  <si>
+    <t>狂战士</t>
+  </si>
+  <si>
+    <t>App_0_03</t>
+  </si>
+  <si>
+    <t>Class_Longbowman</t>
+  </si>
+  <si>
+    <t>长弓手</t>
+  </si>
+  <si>
+    <t>App_0_13</t>
+  </si>
+  <si>
+    <t>Class_FireMage</t>
+  </si>
+  <si>
+    <t>火法</t>
+  </si>
+  <si>
+    <t>App_0_23</t>
+  </si>
+  <si>
+    <t>Class_Shadowblade</t>
+  </si>
+  <si>
+    <t>影刃</t>
+  </si>
+  <si>
+    <t>App_0_33</t>
+  </si>
+  <si>
+    <t>Class_Paladin</t>
+  </si>
+  <si>
+    <t>圣骑士</t>
+  </si>
+  <si>
+    <t>1.5</t>
+  </si>
+  <si>
+    <t>App_4_41</t>
+  </si>
+  <si>
+    <t>Class_DarkMage</t>
+  </si>
+  <si>
+    <t>暗黑法师</t>
+  </si>
+  <si>
+    <t>App_5_51</t>
+  </si>
+  <si>
+    <t>Class_Knight</t>
+  </si>
+  <si>
+    <t>骑士</t>
+  </si>
+  <si>
+    <t>App_05</t>
+  </si>
+  <si>
+    <t>Class_Priest</t>
+  </si>
+  <si>
+    <t>牧师</t>
+  </si>
+  <si>
+    <t>1.2</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>App_09</t>
+  </si>
+  <si>
+    <t>Class_Ranger</t>
+  </si>
+  <si>
+    <t>游侠</t>
+  </si>
+  <si>
+    <t>1.1</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>7</t>
   </si>
   <si>
     <t>App_03</t>
   </si>
   <si>
-    <t>Class_Mage</t>
-  </si>
-  <si>
-    <t>法师</t>
-  </si>
-  <si>
-    <t>Intelligence</t>
-  </si>
-  <si>
-    <t>0.8</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>App_92</t>
-  </si>
-  <si>
-    <t>Class_Knight</t>
-  </si>
-  <si>
-    <t>骑士</t>
-  </si>
-  <si>
-    <t>App_05</t>
-  </si>
-  <si>
-    <t>Class_Rogue</t>
-  </si>
-  <si>
-    <t>盗贼</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>App_07</t>
-  </si>
-  <si>
-    <t>Class_Priest</t>
-  </si>
-  <si>
-    <t>牧师</t>
-  </si>
-  <si>
-    <t>1.2</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>App_09</t>
-  </si>
-  <si>
-    <t>Class_Berserker</t>
-  </si>
-  <si>
-    <t>狂战士</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>App_04</t>
-  </si>
-  <si>
-    <t>Class_Ranger</t>
-  </si>
-  <si>
-    <t>游侠</t>
-  </si>
-  <si>
-    <t>1.1</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
     <t>Class_Warlock</t>
   </si>
   <si>
@@ -302,18 +377,6 @@
   </si>
   <si>
     <t>App_08</t>
-  </si>
-  <si>
-    <t>Class_Paladin</t>
-  </si>
-  <si>
-    <t>圣骑士</t>
-  </si>
-  <si>
-    <t>1.5</t>
-  </si>
-  <si>
-    <t>App_06</t>
   </si>
   <si>
     <t>Class_Servants</t>
@@ -501,12 +564,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -825,7 +900,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -849,16 +924,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -867,92 +942,103 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1299,8 +1385,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="14.75" customWidth="1"/>
+    <col min="4" max="4" width="18.125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" t="s">
@@ -1378,41 +1468,41 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
-      <c r="A3" t="s">
+    <row r="3" s="1" customFormat="1" spans="1:12">
+      <c r="A3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="K3" t="s">
+      <c r="K3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="L3" t="s">
+      <c r="L3" s="1" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1447,10 +1537,10 @@
       <c r="J4" t="s">
         <v>44</v>
       </c>
-      <c r="K4" t="s">
+      <c r="K4" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="L4" s="3" t="s">
         <v>46</v>
       </c>
     </row>
@@ -1485,34 +1575,34 @@
       <c r="J5" t="s">
         <v>51</v>
       </c>
-      <c r="K5" t="s">
+      <c r="K5" s="2">
+        <v>4</v>
+      </c>
+      <c r="L5" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="6" ht="14.25" spans="1:12">
       <c r="A6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" t="s">
         <v>54</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>55</v>
-      </c>
-      <c r="C6" t="s">
-        <v>56</v>
       </c>
       <c r="D6" t="s">
         <v>39</v>
       </c>
       <c r="E6" t="s">
+        <v>56</v>
+      </c>
+      <c r="F6" t="s">
+        <v>41</v>
+      </c>
+      <c r="G6" t="s">
         <v>57</v>
-      </c>
-      <c r="F6" t="s">
-        <v>41</v>
-      </c>
-      <c r="G6" t="s">
-        <v>58</v>
       </c>
       <c r="H6" t="s">
         <v>45</v>
@@ -1523,22 +1613,22 @@
       <c r="J6" t="s">
         <v>51</v>
       </c>
-      <c r="K6" t="s">
-        <v>59</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>60</v>
+      <c r="K6" s="2">
+        <v>3</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="7" ht="14.25" spans="1:12">
       <c r="A7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="D7" t="s">
         <v>39</v>
@@ -1556,27 +1646,27 @@
         <v>42</v>
       </c>
       <c r="I7" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="J7" t="s">
         <v>44</v>
       </c>
-      <c r="K7" t="s">
-        <v>43</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>63</v>
+      <c r="K7" s="2">
+        <v>2</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="8" ht="14.25" spans="1:12">
       <c r="A8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="B8" t="s">
-        <v>65</v>
-      </c>
       <c r="C8" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="D8" t="s">
         <v>39</v>
@@ -1594,42 +1684,42 @@
         <v>42</v>
       </c>
       <c r="I8" t="s">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="J8" t="s">
         <v>44</v>
       </c>
-      <c r="K8" t="s">
-        <v>67</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>68</v>
+      <c r="K8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="9" ht="14.25" spans="1:12">
       <c r="A9" t="s">
-        <v>69</v>
-      </c>
-      <c r="B9" t="s">
-        <v>70</v>
+        <v>66</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>67</v>
       </c>
       <c r="C9" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D9" t="s">
         <v>39</v>
       </c>
       <c r="E9" t="s">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="F9" t="s">
         <v>41</v>
       </c>
       <c r="G9" t="s">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="H9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I9" t="s">
         <v>41</v>
@@ -1637,201 +1727,505 @@
       <c r="J9" t="s">
         <v>51</v>
       </c>
-      <c r="K9" t="s">
-        <v>73</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>74</v>
+      <c r="K9" s="2">
+        <v>4</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="10" ht="14.25" spans="1:12">
       <c r="A10" t="s">
-        <v>75</v>
-      </c>
-      <c r="B10" t="s">
-        <v>76</v>
+        <v>69</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>70</v>
       </c>
       <c r="C10" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="D10" t="s">
         <v>39</v>
       </c>
       <c r="E10" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="F10" t="s">
         <v>41</v>
       </c>
       <c r="G10" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="H10" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="I10" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="J10" t="s">
-        <v>44</v>
-      </c>
-      <c r="K10" t="s">
-        <v>77</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>78</v>
+        <v>51</v>
+      </c>
+      <c r="K10" s="2">
+        <v>3</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="11" ht="14.25" spans="1:12">
       <c r="A11" t="s">
-        <v>79</v>
-      </c>
-      <c r="B11" t="s">
-        <v>80</v>
+        <v>72</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>73</v>
       </c>
       <c r="C11" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="D11" t="s">
         <v>39</v>
       </c>
       <c r="E11" t="s">
-        <v>81</v>
+        <v>40</v>
       </c>
       <c r="F11" t="s">
         <v>41</v>
       </c>
       <c r="G11" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="H11" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="I11" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="J11" t="s">
-        <v>51</v>
-      </c>
-      <c r="K11" t="s">
-        <v>83</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>53</v>
+        <v>44</v>
+      </c>
+      <c r="K11" s="2">
+        <v>2</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="12" ht="14.25" spans="1:12">
       <c r="A12" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="B12" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="C12" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="D12" t="s">
         <v>39</v>
       </c>
       <c r="E12" t="s">
-        <v>86</v>
+        <v>40</v>
       </c>
       <c r="F12" t="s">
         <v>41</v>
       </c>
       <c r="G12" t="s">
-        <v>87</v>
+        <v>42</v>
       </c>
       <c r="H12" t="s">
+        <v>42</v>
+      </c>
+      <c r="I12" t="s">
+        <v>43</v>
+      </c>
+      <c r="J12" t="s">
+        <v>44</v>
+      </c>
+      <c r="K12" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="I12" t="s">
-        <v>45</v>
-      </c>
-      <c r="J12" t="s">
-        <v>51</v>
-      </c>
-      <c r="K12" t="s">
-        <v>88</v>
-      </c>
-      <c r="L12" s="1" t="s">
-        <v>89</v>
+      <c r="L12" s="3" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="13" ht="14.25" spans="1:12">
       <c r="A13" t="s">
-        <v>90</v>
-      </c>
-      <c r="B13" t="s">
-        <v>91</v>
+        <v>78</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>79</v>
       </c>
       <c r="C13" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="D13" t="s">
         <v>39</v>
       </c>
       <c r="E13" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F13" t="s">
         <v>41</v>
       </c>
       <c r="G13" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="H13" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="I13" t="s">
-        <v>92</v>
+        <v>41</v>
       </c>
       <c r="J13" t="s">
-        <v>44</v>
-      </c>
-      <c r="K13" t="s">
-        <v>66</v>
-      </c>
-      <c r="L13" s="1" t="s">
-        <v>93</v>
+        <v>51</v>
+      </c>
+      <c r="K13" s="2">
+        <v>4</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>80</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" ht="14.25" spans="1:12">
       <c r="A14" t="s">
-        <v>94</v>
-      </c>
-      <c r="B14" t="s">
-        <v>95</v>
+        <v>81</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>82</v>
       </c>
       <c r="C14" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="D14" t="s">
         <v>39</v>
       </c>
       <c r="E14" t="s">
+        <v>56</v>
+      </c>
+      <c r="F14" t="s">
+        <v>41</v>
+      </c>
+      <c r="G14" t="s">
+        <v>57</v>
+      </c>
+      <c r="H14" t="s">
+        <v>45</v>
+      </c>
+      <c r="I14" t="s">
+        <v>41</v>
+      </c>
+      <c r="J14" t="s">
+        <v>51</v>
+      </c>
+      <c r="K14" s="2">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="15" ht="14.25" spans="1:12">
+      <c r="A15" t="s">
+        <v>84</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C15" t="s">
+        <v>55</v>
+      </c>
+      <c r="D15" t="s">
+        <v>39</v>
+      </c>
+      <c r="E15" t="s">
         <v>40</v>
       </c>
-      <c r="F14" t="s">
-        <v>41</v>
-      </c>
-      <c r="G14" t="s">
+      <c r="F15" t="s">
+        <v>41</v>
+      </c>
+      <c r="G15" t="s">
         <v>42</v>
       </c>
-      <c r="H14" t="s">
+      <c r="H15" t="s">
         <v>42</v>
       </c>
-      <c r="I14" t="s">
+      <c r="I15" t="s">
+        <v>43</v>
+      </c>
+      <c r="J15" t="s">
+        <v>44</v>
+      </c>
+      <c r="K15" s="2">
+        <v>2</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16" t="s">
+        <v>87</v>
+      </c>
+      <c r="B16" t="s">
+        <v>88</v>
+      </c>
+      <c r="C16" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" t="s">
+        <v>39</v>
+      </c>
+      <c r="E16" t="s">
+        <v>41</v>
+      </c>
+      <c r="F16" t="s">
+        <v>41</v>
+      </c>
+      <c r="G16" t="s">
+        <v>42</v>
+      </c>
+      <c r="H16" t="s">
+        <v>42</v>
+      </c>
+      <c r="I16" t="s">
+        <v>89</v>
+      </c>
+      <c r="J16" t="s">
+        <v>44</v>
+      </c>
+      <c r="K16" s="2">
+        <v>1</v>
+      </c>
+      <c r="L16" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="17" ht="14.25" spans="1:12">
+      <c r="A17" t="s">
+        <v>91</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" t="s">
+        <v>39</v>
+      </c>
+      <c r="E17" t="s">
+        <v>56</v>
+      </c>
+      <c r="F17" t="s">
+        <v>41</v>
+      </c>
+      <c r="G17" t="s">
+        <v>57</v>
+      </c>
+      <c r="H17" t="s">
+        <v>45</v>
+      </c>
+      <c r="I17" t="s">
+        <v>41</v>
+      </c>
+      <c r="J17" t="s">
+        <v>51</v>
+      </c>
+      <c r="K17" s="2">
+        <v>2</v>
+      </c>
+      <c r="L17" s="4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="18" ht="14.25" spans="1:12">
+      <c r="A18" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="K18" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="L18" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="J14" t="s">
+    </row>
+    <row r="19" ht="14.25" spans="1:12">
+      <c r="A19" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="K19" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="L19" s="7" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="20" ht="14.25" spans="1:12">
+      <c r="A20" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="J20" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="K20" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="L20" s="7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="21" ht="14.25" spans="1:12">
+      <c r="A21" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="K21" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="L21" s="7" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="A22" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="J22" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="K14" t="s">
-        <v>97</v>
-      </c>
-      <c r="L14" t="s">
-        <v>98</v>
+      <c r="K22" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="L22" s="5" t="s">
+        <v>119</v>
       </c>
     </row>
   </sheetData>

--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/制造_职业配置表_Manufacture_ClassConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/制造_职业配置表_Manufacture_ClassConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="142">
   <si>
     <t>职业ID</t>
   </si>
@@ -40,6 +40,12 @@
     <t>职业名</t>
   </si>
   <si>
+    <t>基础职业</t>
+  </si>
+  <si>
+    <t>等级</t>
+  </si>
+  <si>
     <t>主属性</t>
   </si>
   <si>
@@ -70,12 +76,21 @@
     <t>职业默认外观</t>
   </si>
   <si>
+    <t>制造默认获得技能ID</t>
+  </si>
+  <si>
     <t>主键；被 SoulConfig.ClassId 引用</t>
   </si>
   <si>
     <t>参与 WarriorName；外观 ClassAffinity 匹配键</t>
   </si>
   <si>
+    <t>CSV 中文：战士|射手|法师|盗贼 → 枚举；空/非法→Unspecified；预留后续魔法书等条件；不参与命名/外观/PrimaryStat/战斗；不烘进实例</t>
+  </si>
+  <si>
+    <t>≥0；仅 UI 展示（UI-016 士兵卡职业名下 Lv.{ClassLevel}）；不参与战斗/制造公式；缺/空 → 0</t>
+  </si>
+  <si>
     <t>Strength|Agility|Intelligence</t>
   </si>
   <si>
@@ -106,12 +121,21 @@
     <t>FK → BodyAppearanceConfig；空则种族 IsFallback</t>
   </si>
   <si>
+    <t>空=无；SkillId 或 SkillId|SkillId；FK → SkillConfig.SkillId</t>
+  </si>
+  <si>
     <t>ClassId</t>
   </si>
   <si>
     <t>ClassName</t>
   </si>
   <si>
+    <t>BaseClass</t>
+  </si>
+  <si>
+    <t>ClassLevel</t>
+  </si>
+  <si>
     <t>PrimaryStat</t>
   </si>
   <si>
@@ -142,84 +166,123 @@
     <t>DefaultAppearanceId</t>
   </si>
   <si>
+    <t>DefaultSkillIds</t>
+  </si>
+  <si>
+    <t>Class_Warrior_0</t>
+  </si>
+  <si>
+    <t>战士</t>
+  </si>
+  <si>
+    <t>Strength</t>
+  </si>
+  <si>
+    <t>NormalAttackPrimaryMult_15|AttackSpeedBase_0.5|AttackSpeedAgiDiv_60|SkillCdIntDiv_30|SkillCdFloor_0.1</t>
+  </si>
+  <si>
+    <t>0.5</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Melee</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>App_0_00</t>
+  </si>
+  <si>
+    <t>Skill_01</t>
+  </si>
+  <si>
+    <t>Class_Archer_0</t>
+  </si>
+  <si>
+    <t>射手</t>
+  </si>
+  <si>
+    <t>Agility</t>
+  </si>
+  <si>
+    <t>NormalAttackPrimaryMult_15|AttackSpeedBase_0.5|AttackSpeedAgiDiv_60|30_30|0.1_0.1</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>Ranged</t>
+  </si>
+  <si>
+    <t>App_0_10</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Class_Mage_0</t>
+  </si>
+  <si>
+    <t>法师</t>
+  </si>
+  <si>
+    <t>Intelligence</t>
+  </si>
+  <si>
+    <t>0.8</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>App_0_20</t>
+  </si>
+  <si>
+    <t>Class_Rogue_0</t>
+  </si>
+  <si>
+    <t>盗贼</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>App_0_30</t>
+  </si>
+  <si>
     <t>Class_Warrior</t>
   </si>
   <si>
-    <t>战士</t>
-  </si>
-  <si>
-    <t>Strength</t>
-  </si>
-  <si>
-    <t>NormalAttackPrimaryMult_15|AttackSpeedBase_0.5|AttackSpeedAgiDiv_60|SkillCdIntDiv_30|SkillCdFloor_0.1</t>
+    <t>NormalAttackPrimaryMult_30|AttackSpeedBase_0.5|AttackSpeedAgiDiv_60|30_30|0.1_0.1</t>
   </si>
   <si>
     <t>0.3</t>
   </si>
   <si>
-    <t>0.5</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>Melee</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
     <t>App_0_01</t>
   </si>
   <si>
     <t>Class_Archer</t>
   </si>
   <si>
-    <t>射手</t>
-  </si>
-  <si>
-    <t>Agility</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>Ranged</t>
-  </si>
-  <si>
     <t>App_0_11</t>
   </si>
   <si>
     <t>Class_Mage</t>
   </si>
   <si>
-    <t>法师</t>
-  </si>
-  <si>
-    <t>Intelligence</t>
-  </si>
-  <si>
-    <t>0.8</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
     <t>App_0_21</t>
   </si>
   <si>
     <t>Class_Rogue</t>
   </si>
   <si>
-    <t>盗贼</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
     <t>App_0_31</t>
   </si>
   <si>
@@ -229,6 +292,9 @@
     <t>近卫</t>
   </si>
   <si>
+    <t>NormalAttackPrimaryMult_45|AttackSpeedBase_0.5|AttackSpeedAgiDiv_60|30_30|0.1_0.1</t>
+  </si>
+  <si>
     <t>App_0_02</t>
   </si>
   <si>
@@ -301,6 +367,9 @@
     <t>圣骑士</t>
   </si>
   <si>
+    <t>NormalAttackPrimaryMult_60|AttackSpeedBase_0.5|AttackSpeedAgiDiv_60|30_30|0.1_0.1</t>
+  </si>
+  <si>
     <t>1.5</t>
   </si>
   <si>
@@ -389,9 +458,6 @@
   </si>
   <si>
     <t>11</t>
-  </si>
-  <si>
-    <t/>
   </si>
 </sst>
 </file>
@@ -564,7 +630,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -574,6 +640,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -879,166 +951,167 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="35" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1385,14 +1458,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:O26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="14.75" customWidth="1"/>
-    <col min="4" max="4" width="18.125" customWidth="1"/>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="3" max="3" width="9.5" customWidth="1"/>
+    <col min="4" max="4" width="15.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1429,803 +1503,1189 @@
       <c r="L1" t="s">
         <v>11</v>
       </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L2" t="s">
-        <v>23</v>
+        <v>26</v>
+      </c>
+      <c r="M2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O2" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:12">
+    <row r="3" s="1" customFormat="1" spans="1:15">
       <c r="A3" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>44</v>
       </c>
     </row>
-    <row r="4" ht="14.25" spans="1:12">
+    <row r="4" ht="14.25" customHeight="1" spans="1:15">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="B4" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D4" t="s">
-        <v>39</v>
+        <v>46</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>40</v>
-      </c>
-      <c r="F4" t="s">
-        <v>41</v>
-      </c>
-      <c r="G4" t="s">
-        <v>42</v>
+        <v>47</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="G4">
+        <v>0.35</v>
       </c>
       <c r="H4" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="I4" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="J4" t="s">
-        <v>44</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="L4" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="K4" t="s">
+        <v>51</v>
+      </c>
+      <c r="L4" t="s">
+        <v>52</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="O4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5" ht="14.25" customHeight="1" spans="1:15">
+      <c r="A5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5" t="s">
+        <v>58</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H5" t="s">
+        <v>49</v>
+      </c>
+      <c r="I5" t="s">
+        <v>60</v>
+      </c>
+      <c r="J5" t="s">
+        <v>53</v>
+      </c>
+      <c r="K5" t="s">
+        <v>49</v>
+      </c>
+      <c r="L5" t="s">
+        <v>61</v>
+      </c>
+      <c r="M5" s="3">
+        <v>4</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="O5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" ht="14.25" customHeight="1" spans="1:15">
+      <c r="A6" t="s">
+        <v>64</v>
+      </c>
+      <c r="B6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6" t="s">
+        <v>66</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G6" t="s">
+        <v>67</v>
+      </c>
+      <c r="H6" t="s">
+        <v>49</v>
+      </c>
+      <c r="I6" t="s">
+        <v>68</v>
+      </c>
+      <c r="J6" t="s">
+        <v>53</v>
+      </c>
+      <c r="K6" t="s">
+        <v>49</v>
+      </c>
+      <c r="L6" t="s">
+        <v>61</v>
+      </c>
+      <c r="M6" s="3">
+        <v>3</v>
+      </c>
+      <c r="N6" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="O6" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" ht="14.25" customHeight="1" spans="1:15">
+      <c r="A7" t="s">
+        <v>70</v>
+      </c>
+      <c r="B7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7" t="s">
+        <v>58</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G7">
+        <v>0.35</v>
+      </c>
+      <c r="H7" t="s">
+        <v>49</v>
+      </c>
+      <c r="I7" t="s">
+        <v>50</v>
+      </c>
+      <c r="J7" t="s">
+        <v>50</v>
+      </c>
+      <c r="K7" t="s">
+        <v>72</v>
+      </c>
+      <c r="L7" t="s">
+        <v>52</v>
+      </c>
+      <c r="M7" s="3">
+        <v>2</v>
+      </c>
+      <c r="N7" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="O7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" ht="14.25" customHeight="1" spans="1:15">
+      <c r="A8" t="s">
+        <v>74</v>
+      </c>
+      <c r="B8" t="s">
         <v>46</v>
       </c>
+      <c r="C8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8">
+        <v>2</v>
+      </c>
+      <c r="E8" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G8" t="s">
+        <v>76</v>
+      </c>
+      <c r="H8" t="s">
+        <v>49</v>
+      </c>
+      <c r="I8" t="s">
+        <v>50</v>
+      </c>
+      <c r="J8" t="s">
+        <v>50</v>
+      </c>
+      <c r="K8" t="s">
+        <v>51</v>
+      </c>
+      <c r="L8" t="s">
+        <v>52</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="N8" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="O8" t="s">
+        <v>55</v>
+      </c>
     </row>
-    <row r="5" ht="14.25" spans="1:12">
-      <c r="A5" t="s">
+    <row r="9" ht="14.25" customHeight="1" spans="1:15">
+      <c r="A9" t="s">
+        <v>78</v>
+      </c>
+      <c r="B9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D9">
+        <v>2</v>
+      </c>
+      <c r="E9" t="s">
+        <v>58</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G9" t="s">
+        <v>53</v>
+      </c>
+      <c r="H9" t="s">
+        <v>49</v>
+      </c>
+      <c r="I9" t="s">
+        <v>60</v>
+      </c>
+      <c r="J9" t="s">
+        <v>53</v>
+      </c>
+      <c r="K9" t="s">
+        <v>49</v>
+      </c>
+      <c r="L9" t="s">
+        <v>61</v>
+      </c>
+      <c r="M9" s="3">
+        <v>4</v>
+      </c>
+      <c r="N9" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="O9" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="10" ht="14.25" customHeight="1" spans="1:15">
+      <c r="A10" t="s">
+        <v>80</v>
+      </c>
+      <c r="B10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C10" t="s">
+        <v>65</v>
+      </c>
+      <c r="D10">
+        <v>2</v>
+      </c>
+      <c r="E10" t="s">
+        <v>66</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G10" t="s">
+        <v>67</v>
+      </c>
+      <c r="H10" t="s">
+        <v>49</v>
+      </c>
+      <c r="I10" t="s">
+        <v>68</v>
+      </c>
+      <c r="J10" t="s">
+        <v>53</v>
+      </c>
+      <c r="K10" t="s">
+        <v>49</v>
+      </c>
+      <c r="L10" t="s">
+        <v>61</v>
+      </c>
+      <c r="M10" s="3">
+        <v>3</v>
+      </c>
+      <c r="N10" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="O10" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" ht="14.25" customHeight="1" spans="1:15">
+      <c r="A11" t="s">
+        <v>82</v>
+      </c>
+      <c r="B11" t="s">
+        <v>71</v>
+      </c>
+      <c r="C11" t="s">
+        <v>71</v>
+      </c>
+      <c r="D11">
+        <v>2</v>
+      </c>
+      <c r="E11" t="s">
+        <v>58</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G11">
+        <v>0.35</v>
+      </c>
+      <c r="H11" t="s">
+        <v>49</v>
+      </c>
+      <c r="I11" t="s">
+        <v>50</v>
+      </c>
+      <c r="J11" t="s">
+        <v>50</v>
+      </c>
+      <c r="K11" t="s">
+        <v>72</v>
+      </c>
+      <c r="L11" t="s">
+        <v>52</v>
+      </c>
+      <c r="M11" s="3">
+        <v>2</v>
+      </c>
+      <c r="N11" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="O11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" ht="14.25" customHeight="1" spans="1:15">
+      <c r="A12" t="s">
+        <v>84</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C12" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12">
+        <v>3</v>
+      </c>
+      <c r="E12" t="s">
         <v>47</v>
       </c>
-      <c r="B5" t="s">
+      <c r="F12" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G12">
+        <v>0.35</v>
+      </c>
+      <c r="H12" t="s">
+        <v>49</v>
+      </c>
+      <c r="I12" t="s">
+        <v>50</v>
+      </c>
+      <c r="J12" t="s">
+        <v>50</v>
+      </c>
+      <c r="K12" t="s">
+        <v>51</v>
+      </c>
+      <c r="L12" t="s">
+        <v>52</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="N12" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="O12" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="13" ht="14.25" customHeight="1" spans="1:15">
+      <c r="A13" t="s">
+        <v>88</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C13" t="s">
+        <v>57</v>
+      </c>
+      <c r="D13">
+        <v>3</v>
+      </c>
+      <c r="E13" t="s">
+        <v>58</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G13" t="s">
+        <v>53</v>
+      </c>
+      <c r="H13" t="s">
+        <v>49</v>
+      </c>
+      <c r="I13" t="s">
+        <v>60</v>
+      </c>
+      <c r="J13" t="s">
+        <v>53</v>
+      </c>
+      <c r="K13" t="s">
+        <v>49</v>
+      </c>
+      <c r="L13" t="s">
+        <v>61</v>
+      </c>
+      <c r="M13" s="3">
+        <v>4</v>
+      </c>
+      <c r="N13" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="O13" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="14" ht="14.25" customHeight="1" spans="1:15">
+      <c r="A14" t="s">
+        <v>91</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="C14" t="s">
+        <v>65</v>
+      </c>
+      <c r="D14">
+        <v>3</v>
+      </c>
+      <c r="E14" t="s">
+        <v>66</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G14" t="s">
+        <v>67</v>
+      </c>
+      <c r="H14" t="s">
+        <v>49</v>
+      </c>
+      <c r="I14" t="s">
+        <v>68</v>
+      </c>
+      <c r="J14" t="s">
+        <v>53</v>
+      </c>
+      <c r="K14" t="s">
+        <v>49</v>
+      </c>
+      <c r="L14" t="s">
+        <v>61</v>
+      </c>
+      <c r="M14" s="3">
+        <v>3</v>
+      </c>
+      <c r="N14" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="O14" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="15" ht="14.25" customHeight="1" spans="1:15">
+      <c r="A15" t="s">
+        <v>94</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C15" t="s">
+        <v>71</v>
+      </c>
+      <c r="D15">
+        <v>3</v>
+      </c>
+      <c r="E15" t="s">
+        <v>47</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G15">
+        <v>0.35</v>
+      </c>
+      <c r="H15" t="s">
+        <v>49</v>
+      </c>
+      <c r="I15" t="s">
+        <v>50</v>
+      </c>
+      <c r="J15" t="s">
+        <v>50</v>
+      </c>
+      <c r="K15" t="s">
+        <v>51</v>
+      </c>
+      <c r="L15" t="s">
+        <v>52</v>
+      </c>
+      <c r="M15" s="3">
+        <v>2</v>
+      </c>
+      <c r="N15" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="O15" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="16" ht="14.25" customHeight="1" spans="1:15">
+      <c r="A16" t="s">
+        <v>97</v>
+      </c>
+      <c r="B16" t="s">
+        <v>98</v>
+      </c>
+      <c r="C16" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16">
+        <v>3</v>
+      </c>
+      <c r="E16" t="s">
+        <v>47</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G16">
+        <v>0.35</v>
+      </c>
+      <c r="H16" t="s">
+        <v>49</v>
+      </c>
+      <c r="I16" t="s">
+        <v>50</v>
+      </c>
+      <c r="J16" t="s">
+        <v>50</v>
+      </c>
+      <c r="K16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="N16" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="O16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="17" ht="14.25" customHeight="1" spans="1:15">
+      <c r="A17" t="s">
+        <v>100</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C17" t="s">
+        <v>57</v>
+      </c>
+      <c r="D17">
+        <v>3</v>
+      </c>
+      <c r="E17" t="s">
+        <v>58</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G17" t="s">
+        <v>53</v>
+      </c>
+      <c r="H17" t="s">
+        <v>49</v>
+      </c>
+      <c r="I17" t="s">
+        <v>60</v>
+      </c>
+      <c r="J17" t="s">
+        <v>53</v>
+      </c>
+      <c r="K17" t="s">
+        <v>49</v>
+      </c>
+      <c r="L17" t="s">
+        <v>61</v>
+      </c>
+      <c r="M17" s="3">
+        <v>4</v>
+      </c>
+      <c r="N17" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="O17" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="18" ht="14.25" customHeight="1" spans="1:15">
+      <c r="A18" t="s">
+        <v>103</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C18" t="s">
+        <v>65</v>
+      </c>
+      <c r="D18">
+        <v>3</v>
+      </c>
+      <c r="E18" t="s">
+        <v>66</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G18" t="s">
+        <v>67</v>
+      </c>
+      <c r="H18" t="s">
+        <v>49</v>
+      </c>
+      <c r="I18" t="s">
+        <v>68</v>
+      </c>
+      <c r="J18" t="s">
+        <v>53</v>
+      </c>
+      <c r="K18" t="s">
+        <v>49</v>
+      </c>
+      <c r="L18" t="s">
+        <v>61</v>
+      </c>
+      <c r="M18" s="3">
+        <v>3</v>
+      </c>
+      <c r="N18" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="O18" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="19" ht="14.25" customHeight="1" spans="1:15">
+      <c r="A19" t="s">
+        <v>106</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C19" t="s">
+        <v>71</v>
+      </c>
+      <c r="D19">
+        <v>3</v>
+      </c>
+      <c r="E19" t="s">
+        <v>66</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G19">
+        <v>0.35</v>
+      </c>
+      <c r="H19" t="s">
+        <v>49</v>
+      </c>
+      <c r="I19" t="s">
+        <v>50</v>
+      </c>
+      <c r="J19" t="s">
+        <v>50</v>
+      </c>
+      <c r="K19" t="s">
+        <v>51</v>
+      </c>
+      <c r="L19" t="s">
+        <v>52</v>
+      </c>
+      <c r="M19" s="3">
+        <v>2</v>
+      </c>
+      <c r="N19" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="O19" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15">
+      <c r="A20" t="s">
+        <v>109</v>
+      </c>
+      <c r="B20" t="s">
+        <v>110</v>
+      </c>
+      <c r="C20" t="s">
+        <v>46</v>
+      </c>
+      <c r="D20">
+        <v>4</v>
+      </c>
+      <c r="E20" t="s">
+        <v>47</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="G20" t="s">
+        <v>49</v>
+      </c>
+      <c r="H20" t="s">
+        <v>49</v>
+      </c>
+      <c r="I20" t="s">
+        <v>50</v>
+      </c>
+      <c r="J20" t="s">
+        <v>50</v>
+      </c>
+      <c r="K20" t="s">
+        <v>112</v>
+      </c>
+      <c r="L20" t="s">
+        <v>52</v>
+      </c>
+      <c r="M20" s="3">
+        <v>1</v>
+      </c>
+      <c r="N20" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="O20" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="21" ht="14.25" customHeight="1" spans="1:15">
+      <c r="A21" t="s">
+        <v>114</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C21" t="s">
+        <v>65</v>
+      </c>
+      <c r="D21">
+        <v>4</v>
+      </c>
+      <c r="E21" t="s">
+        <v>66</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="G21" t="s">
+        <v>67</v>
+      </c>
+      <c r="H21" t="s">
+        <v>49</v>
+      </c>
+      <c r="I21" t="s">
+        <v>68</v>
+      </c>
+      <c r="J21" t="s">
+        <v>53</v>
+      </c>
+      <c r="K21" t="s">
+        <v>49</v>
+      </c>
+      <c r="L21" t="s">
+        <v>61</v>
+      </c>
+      <c r="M21" s="3">
+        <v>2</v>
+      </c>
+      <c r="N21" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="O21" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="22" ht="14.25" customHeight="1" spans="1:15">
+      <c r="A22" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C22" t="s">
+        <v>46</v>
+      </c>
+      <c r="D22" s="6">
+        <v>1</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F22" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="C5" t="s">
-        <v>49</v>
-      </c>
-      <c r="D5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F5" t="s">
-        <v>41</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="G22" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="I22" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="H5" t="s">
-        <v>45</v>
-      </c>
-      <c r="I5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J5" t="s">
+      <c r="J22" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="K22" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="K5" s="2">
-        <v>4</v>
-      </c>
-      <c r="L5" s="3" t="s">
+      <c r="L22" s="6" t="s">
         <v>52</v>
       </c>
+      <c r="M22" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="N22" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="O22" t="s">
+        <v>63</v>
+      </c>
     </row>
-    <row r="6" ht="14.25" spans="1:12">
-      <c r="A6" t="s">
+    <row r="23" ht="14.25" customHeight="1" spans="1:15">
+      <c r="A23" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="C23" t="s">
+        <v>65</v>
+      </c>
+      <c r="D23" s="6">
+        <v>1</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="J23" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="K23" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="L23" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="M23" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="N23" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="O23" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="24" ht="14.25" customHeight="1" spans="1:15">
+      <c r="A24" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="C24" t="s">
+        <v>57</v>
+      </c>
+      <c r="D24" s="6">
+        <v>1</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="J24" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B6" t="s">
-        <v>54</v>
-      </c>
-      <c r="C6" t="s">
-        <v>55</v>
-      </c>
-      <c r="D6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E6" t="s">
-        <v>56</v>
-      </c>
-      <c r="F6" t="s">
-        <v>41</v>
-      </c>
-      <c r="G6" t="s">
-        <v>57</v>
-      </c>
-      <c r="H6" t="s">
-        <v>45</v>
-      </c>
-      <c r="I6" t="s">
-        <v>41</v>
-      </c>
-      <c r="J6" t="s">
-        <v>51</v>
-      </c>
-      <c r="K6" s="2">
-        <v>3</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>58</v>
+      <c r="K24" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="L24" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="M24" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="N24" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="O24" t="s">
+        <v>63</v>
       </c>
     </row>
-    <row r="7" ht="14.25" spans="1:12">
-      <c r="A7" t="s">
-        <v>59</v>
-      </c>
-      <c r="B7" t="s">
-        <v>60</v>
-      </c>
-      <c r="C7" t="s">
-        <v>49</v>
-      </c>
-      <c r="D7" t="s">
-        <v>39</v>
-      </c>
-      <c r="E7" t="s">
-        <v>40</v>
-      </c>
-      <c r="F7" t="s">
-        <v>41</v>
-      </c>
-      <c r="G7" t="s">
-        <v>42</v>
-      </c>
-      <c r="H7" t="s">
-        <v>42</v>
-      </c>
-      <c r="I7" t="s">
+    <row r="25" ht="14.25" customHeight="1" spans="1:15">
+      <c r="A25" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="C25" t="s">
+        <v>65</v>
+      </c>
+      <c r="D25" s="6">
+        <v>1</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="J25" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="K25" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="L25" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="J7" t="s">
-        <v>44</v>
-      </c>
-      <c r="K7" s="2">
-        <v>2</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>62</v>
+      <c r="M25" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="N25" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="O25" t="s">
+        <v>63</v>
       </c>
     </row>
-    <row r="8" ht="14.25" spans="1:12">
-      <c r="A8" t="s">
+    <row r="26" spans="1:15">
+      <c r="A26" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="C26" t="s">
+        <v>46</v>
+      </c>
+      <c r="D26" s="6">
+        <v>1</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="J26" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="K26" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="L26" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="M26" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="N26" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C8" t="s">
-        <v>38</v>
-      </c>
-      <c r="D8" t="s">
-        <v>39</v>
-      </c>
-      <c r="E8" t="s">
-        <v>40</v>
-      </c>
-      <c r="F8" t="s">
-        <v>41</v>
-      </c>
-      <c r="G8" t="s">
-        <v>42</v>
-      </c>
-      <c r="H8" t="s">
-        <v>42</v>
-      </c>
-      <c r="I8" t="s">
-        <v>43</v>
-      </c>
-      <c r="J8" t="s">
-        <v>44</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="9" ht="14.25" spans="1:12">
-      <c r="A9" t="s">
-        <v>66</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C9" t="s">
-        <v>49</v>
-      </c>
-      <c r="D9" t="s">
-        <v>39</v>
-      </c>
-      <c r="E9" t="s">
-        <v>45</v>
-      </c>
-      <c r="F9" t="s">
-        <v>41</v>
-      </c>
-      <c r="G9" t="s">
-        <v>50</v>
-      </c>
-      <c r="H9" t="s">
-        <v>45</v>
-      </c>
-      <c r="I9" t="s">
-        <v>41</v>
-      </c>
-      <c r="J9" t="s">
-        <v>51</v>
-      </c>
-      <c r="K9" s="2">
-        <v>4</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="10" ht="14.25" spans="1:12">
-      <c r="A10" t="s">
-        <v>69</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C10" t="s">
-        <v>55</v>
-      </c>
-      <c r="D10" t="s">
-        <v>39</v>
-      </c>
-      <c r="E10" t="s">
-        <v>56</v>
-      </c>
-      <c r="F10" t="s">
-        <v>41</v>
-      </c>
-      <c r="G10" t="s">
-        <v>57</v>
-      </c>
-      <c r="H10" t="s">
-        <v>45</v>
-      </c>
-      <c r="I10" t="s">
-        <v>41</v>
-      </c>
-      <c r="J10" t="s">
-        <v>51</v>
-      </c>
-      <c r="K10" s="2">
-        <v>3</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="11" ht="14.25" spans="1:12">
-      <c r="A11" t="s">
-        <v>72</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C11" t="s">
-        <v>38</v>
-      </c>
-      <c r="D11" t="s">
-        <v>39</v>
-      </c>
-      <c r="E11" t="s">
-        <v>40</v>
-      </c>
-      <c r="F11" t="s">
-        <v>41</v>
-      </c>
-      <c r="G11" t="s">
-        <v>42</v>
-      </c>
-      <c r="H11" t="s">
-        <v>42</v>
-      </c>
-      <c r="I11" t="s">
-        <v>43</v>
-      </c>
-      <c r="J11" t="s">
-        <v>44</v>
-      </c>
-      <c r="K11" s="2">
-        <v>2</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="12" ht="14.25" spans="1:12">
-      <c r="A12" t="s">
-        <v>75</v>
-      </c>
-      <c r="B12" t="s">
-        <v>76</v>
-      </c>
-      <c r="C12" t="s">
-        <v>38</v>
-      </c>
-      <c r="D12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E12" t="s">
-        <v>40</v>
-      </c>
-      <c r="F12" t="s">
-        <v>41</v>
-      </c>
-      <c r="G12" t="s">
-        <v>42</v>
-      </c>
-      <c r="H12" t="s">
-        <v>42</v>
-      </c>
-      <c r="I12" t="s">
-        <v>43</v>
-      </c>
-      <c r="J12" t="s">
-        <v>44</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="13" ht="14.25" spans="1:12">
-      <c r="A13" t="s">
-        <v>78</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C13" t="s">
-        <v>49</v>
-      </c>
-      <c r="D13" t="s">
-        <v>39</v>
-      </c>
-      <c r="E13" t="s">
-        <v>45</v>
-      </c>
-      <c r="F13" t="s">
-        <v>41</v>
-      </c>
-      <c r="G13" t="s">
-        <v>50</v>
-      </c>
-      <c r="H13" t="s">
-        <v>45</v>
-      </c>
-      <c r="I13" t="s">
-        <v>41</v>
-      </c>
-      <c r="J13" t="s">
-        <v>51</v>
-      </c>
-      <c r="K13" s="2">
-        <v>4</v>
-      </c>
-      <c r="L13" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="14" ht="14.25" spans="1:12">
-      <c r="A14" t="s">
-        <v>81</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="C14" t="s">
-        <v>55</v>
-      </c>
-      <c r="D14" t="s">
-        <v>39</v>
-      </c>
-      <c r="E14" t="s">
-        <v>56</v>
-      </c>
-      <c r="F14" t="s">
-        <v>41</v>
-      </c>
-      <c r="G14" t="s">
-        <v>57</v>
-      </c>
-      <c r="H14" t="s">
-        <v>45</v>
-      </c>
-      <c r="I14" t="s">
-        <v>41</v>
-      </c>
-      <c r="J14" t="s">
-        <v>51</v>
-      </c>
-      <c r="K14" s="2">
-        <v>3</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="15" ht="14.25" spans="1:12">
-      <c r="A15" t="s">
-        <v>84</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="C15" t="s">
-        <v>55</v>
-      </c>
-      <c r="D15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E15" t="s">
-        <v>40</v>
-      </c>
-      <c r="F15" t="s">
-        <v>41</v>
-      </c>
-      <c r="G15" t="s">
-        <v>42</v>
-      </c>
-      <c r="H15" t="s">
-        <v>42</v>
-      </c>
-      <c r="I15" t="s">
-        <v>43</v>
-      </c>
-      <c r="J15" t="s">
-        <v>44</v>
-      </c>
-      <c r="K15" s="2">
-        <v>2</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12">
-      <c r="A16" t="s">
-        <v>87</v>
-      </c>
-      <c r="B16" t="s">
-        <v>88</v>
-      </c>
-      <c r="C16" t="s">
-        <v>38</v>
-      </c>
-      <c r="D16" t="s">
-        <v>39</v>
-      </c>
-      <c r="E16" t="s">
-        <v>41</v>
-      </c>
-      <c r="F16" t="s">
-        <v>41</v>
-      </c>
-      <c r="G16" t="s">
-        <v>42</v>
-      </c>
-      <c r="H16" t="s">
-        <v>42</v>
-      </c>
-      <c r="I16" t="s">
-        <v>89</v>
-      </c>
-      <c r="J16" t="s">
-        <v>44</v>
-      </c>
-      <c r="K16" s="2">
-        <v>1</v>
-      </c>
-      <c r="L16" s="4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="17" ht="14.25" spans="1:12">
-      <c r="A17" t="s">
-        <v>91</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="C17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D17" t="s">
-        <v>39</v>
-      </c>
-      <c r="E17" t="s">
-        <v>56</v>
-      </c>
-      <c r="F17" t="s">
-        <v>41</v>
-      </c>
-      <c r="G17" t="s">
-        <v>57</v>
-      </c>
-      <c r="H17" t="s">
-        <v>45</v>
-      </c>
-      <c r="I17" t="s">
-        <v>41</v>
-      </c>
-      <c r="J17" t="s">
-        <v>51</v>
-      </c>
-      <c r="K17" s="2">
-        <v>2</v>
-      </c>
-      <c r="L17" s="4" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="18" ht="14.25" spans="1:12">
-      <c r="A18" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="H18" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="I18" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="J18" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="K18" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="L18" s="7" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="19" ht="14.25" spans="1:12">
-      <c r="A19" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="H19" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="I19" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J19" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="K19" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="L19" s="7" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="20" ht="14.25" spans="1:12">
-      <c r="A20" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="H20" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="I20" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="J20" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="K20" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="L20" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="21" ht="14.25" spans="1:12">
-      <c r="A21" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="H21" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="I21" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="J21" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="K21" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="L21" s="7" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12">
-      <c r="A22" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="G22" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="H22" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="I22" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="J22" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="K22" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="L22" s="5" t="s">
-        <v>119</v>
+      <c r="O26" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>

--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/制造_职业配置表_Manufacture_ClassConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/制造_职业配置表_Manufacture_ClassConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="146">
   <si>
     <t>职业ID</t>
   </si>
@@ -259,6 +259,9 @@
     <t>Class_Warrior</t>
   </si>
   <si>
+    <t>战士2</t>
+  </si>
+  <si>
     <t>NormalAttackPrimaryMult_30|AttackSpeedBase_0.5|AttackSpeedAgiDiv_60|30_30|0.1_0.1</t>
   </si>
   <si>
@@ -271,16 +274,25 @@
     <t>Class_Archer</t>
   </si>
   <si>
+    <t>射手2</t>
+  </si>
+  <si>
     <t>App_0_11</t>
   </si>
   <si>
     <t>Class_Mage</t>
   </si>
   <si>
+    <t>法师2</t>
+  </si>
+  <si>
     <t>App_0_21</t>
   </si>
   <si>
     <t>Class_Rogue</t>
+  </si>
+  <si>
+    <t>盗贼2</t>
   </si>
   <si>
     <t>App_0_31</t>
@@ -1096,9 +1108,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1108,6 +1126,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1463,7 +1484,7 @@
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="3" max="3" width="9.5" customWidth="1"/>
-    <col min="4" max="4" width="15.5" customWidth="1"/>
+    <col min="4" max="4" width="15.5" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
@@ -1476,7 +1497,7 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
       <c r="E1" t="s">
@@ -1523,7 +1544,7 @@
       <c r="C2" t="s">
         <v>17</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E2" t="s">
@@ -1570,7 +1591,7 @@
       <c r="C3" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="3" t="s">
         <v>33</v>
       </c>
       <c r="E3" s="1" t="s">
@@ -1617,13 +1638,13 @@
       <c r="C4" t="s">
         <v>46</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="2">
         <v>1</v>
       </c>
       <c r="E4" t="s">
         <v>47</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="4" t="s">
         <v>48</v>
       </c>
       <c r="G4">
@@ -1644,10 +1665,10 @@
       <c r="L4" t="s">
         <v>52</v>
       </c>
-      <c r="M4" s="3" t="s">
+      <c r="M4" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="N4" s="4" t="s">
+      <c r="N4" s="6" t="s">
         <v>54</v>
       </c>
       <c r="O4" t="s">
@@ -1664,13 +1685,13 @@
       <c r="C5" t="s">
         <v>57</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="2">
         <v>1</v>
       </c>
       <c r="E5" t="s">
         <v>58</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="4" t="s">
         <v>59</v>
       </c>
       <c r="G5" t="s">
@@ -1691,10 +1712,10 @@
       <c r="L5" t="s">
         <v>61</v>
       </c>
-      <c r="M5" s="3">
+      <c r="M5" s="5">
         <v>4</v>
       </c>
-      <c r="N5" s="4" t="s">
+      <c r="N5" s="6" t="s">
         <v>62</v>
       </c>
       <c r="O5" t="s">
@@ -1711,13 +1732,13 @@
       <c r="C6" t="s">
         <v>65</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="2">
         <v>1</v>
       </c>
       <c r="E6" t="s">
         <v>66</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="4" t="s">
         <v>59</v>
       </c>
       <c r="G6" t="s">
@@ -1738,10 +1759,10 @@
       <c r="L6" t="s">
         <v>61</v>
       </c>
-      <c r="M6" s="3">
+      <c r="M6" s="5">
         <v>3</v>
       </c>
-      <c r="N6" s="4" t="s">
+      <c r="N6" s="6" t="s">
         <v>69</v>
       </c>
       <c r="O6" t="s">
@@ -1758,13 +1779,13 @@
       <c r="C7" t="s">
         <v>71</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="2">
         <v>1</v>
       </c>
       <c r="E7" t="s">
         <v>58</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="4" t="s">
         <v>59</v>
       </c>
       <c r="G7">
@@ -1785,10 +1806,10 @@
       <c r="L7" t="s">
         <v>52</v>
       </c>
-      <c r="M7" s="3">
+      <c r="M7" s="5">
         <v>2</v>
       </c>
-      <c r="N7" s="4" t="s">
+      <c r="N7" s="6" t="s">
         <v>73</v>
       </c>
       <c r="O7" t="s">
@@ -1800,22 +1821,22 @@
         <v>74</v>
       </c>
       <c r="B8" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="C8" t="s">
         <v>46</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="2">
         <v>2</v>
       </c>
       <c r="E8" t="s">
         <v>47</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>75</v>
+      <c r="F8" s="4" t="s">
+        <v>76</v>
       </c>
       <c r="G8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H8" t="s">
         <v>49</v>
@@ -1832,11 +1853,11 @@
       <c r="L8" t="s">
         <v>52</v>
       </c>
-      <c r="M8" s="3" t="s">
+      <c r="M8" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="N8" s="4" t="s">
-        <v>77</v>
+      <c r="N8" s="6" t="s">
+        <v>78</v>
       </c>
       <c r="O8" t="s">
         <v>55</v>
@@ -1844,22 +1865,22 @@
     </row>
     <row r="9" ht="14.25" customHeight="1" spans="1:15">
       <c r="A9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="C9" t="s">
         <v>57</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="2">
         <v>2</v>
       </c>
       <c r="E9" t="s">
         <v>58</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>75</v>
+      <c r="F9" s="4" t="s">
+        <v>76</v>
       </c>
       <c r="G9" t="s">
         <v>53</v>
@@ -1879,11 +1900,11 @@
       <c r="L9" t="s">
         <v>61</v>
       </c>
-      <c r="M9" s="3">
+      <c r="M9" s="5">
         <v>4</v>
       </c>
-      <c r="N9" s="4" t="s">
-        <v>79</v>
+      <c r="N9" s="6" t="s">
+        <v>81</v>
       </c>
       <c r="O9" t="s">
         <v>63</v>
@@ -1891,22 +1912,22 @@
     </row>
     <row r="10" ht="14.25" customHeight="1" spans="1:15">
       <c r="A10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="C10" t="s">
         <v>65</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="2">
         <v>2</v>
       </c>
       <c r="E10" t="s">
         <v>66</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>75</v>
+      <c r="F10" s="4" t="s">
+        <v>76</v>
       </c>
       <c r="G10" t="s">
         <v>67</v>
@@ -1926,11 +1947,11 @@
       <c r="L10" t="s">
         <v>61</v>
       </c>
-      <c r="M10" s="3">
+      <c r="M10" s="5">
         <v>3</v>
       </c>
-      <c r="N10" s="4" t="s">
-        <v>81</v>
+      <c r="N10" s="6" t="s">
+        <v>84</v>
       </c>
       <c r="O10" t="s">
         <v>63</v>
@@ -1938,22 +1959,22 @@
     </row>
     <row r="11" ht="14.25" customHeight="1" spans="1:15">
       <c r="A11" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B11" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="C11" t="s">
         <v>71</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="2">
         <v>2</v>
       </c>
       <c r="E11" t="s">
         <v>58</v>
       </c>
-      <c r="F11" s="2" t="s">
-        <v>75</v>
+      <c r="F11" s="4" t="s">
+        <v>76</v>
       </c>
       <c r="G11">
         <v>0.35</v>
@@ -1973,11 +1994,11 @@
       <c r="L11" t="s">
         <v>52</v>
       </c>
-      <c r="M11" s="3">
+      <c r="M11" s="5">
         <v>2</v>
       </c>
-      <c r="N11" s="4" t="s">
-        <v>83</v>
+      <c r="N11" s="6" t="s">
+        <v>87</v>
       </c>
       <c r="O11" t="s">
         <v>63</v>
@@ -1985,22 +2006,22 @@
     </row>
     <row r="12" ht="14.25" customHeight="1" spans="1:15">
       <c r="A12" t="s">
-        <v>84</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>85</v>
+        <v>88</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>89</v>
       </c>
       <c r="C12" t="s">
         <v>46</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="2">
         <v>3</v>
       </c>
       <c r="E12" t="s">
         <v>47</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>86</v>
+      <c r="F12" s="4" t="s">
+        <v>90</v>
       </c>
       <c r="G12">
         <v>0.35</v>
@@ -2020,11 +2041,11 @@
       <c r="L12" t="s">
         <v>52</v>
       </c>
-      <c r="M12" s="3" t="s">
+      <c r="M12" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="N12" s="4" t="s">
-        <v>87</v>
+      <c r="N12" s="6" t="s">
+        <v>91</v>
       </c>
       <c r="O12" t="s">
         <v>63</v>
@@ -2032,22 +2053,22 @@
     </row>
     <row r="13" ht="14.25" customHeight="1" spans="1:15">
       <c r="A13" t="s">
-        <v>88</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>89</v>
+        <v>92</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>93</v>
       </c>
       <c r="C13" t="s">
         <v>57</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="2">
         <v>3</v>
       </c>
       <c r="E13" t="s">
         <v>58</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>86</v>
+      <c r="F13" s="4" t="s">
+        <v>90</v>
       </c>
       <c r="G13" t="s">
         <v>53</v>
@@ -2067,11 +2088,11 @@
       <c r="L13" t="s">
         <v>61</v>
       </c>
-      <c r="M13" s="3">
+      <c r="M13" s="5">
         <v>4</v>
       </c>
-      <c r="N13" s="4" t="s">
-        <v>90</v>
+      <c r="N13" s="6" t="s">
+        <v>94</v>
       </c>
       <c r="O13" t="s">
         <v>63</v>
@@ -2079,22 +2100,22 @@
     </row>
     <row r="14" ht="14.25" customHeight="1" spans="1:15">
       <c r="A14" t="s">
-        <v>91</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>92</v>
+        <v>95</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>96</v>
       </c>
       <c r="C14" t="s">
         <v>65</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="2">
         <v>3</v>
       </c>
       <c r="E14" t="s">
         <v>66</v>
       </c>
-      <c r="F14" s="2" t="s">
-        <v>86</v>
+      <c r="F14" s="4" t="s">
+        <v>90</v>
       </c>
       <c r="G14" t="s">
         <v>67</v>
@@ -2114,11 +2135,11 @@
       <c r="L14" t="s">
         <v>61</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="5">
         <v>3</v>
       </c>
-      <c r="N14" s="4" t="s">
-        <v>93</v>
+      <c r="N14" s="6" t="s">
+        <v>97</v>
       </c>
       <c r="O14" t="s">
         <v>63</v>
@@ -2126,22 +2147,22 @@
     </row>
     <row r="15" ht="14.25" customHeight="1" spans="1:15">
       <c r="A15" t="s">
-        <v>94</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>95</v>
+        <v>98</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>99</v>
       </c>
       <c r="C15" t="s">
         <v>71</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="2">
         <v>3</v>
       </c>
       <c r="E15" t="s">
         <v>47</v>
       </c>
-      <c r="F15" s="2" t="s">
-        <v>86</v>
+      <c r="F15" s="4" t="s">
+        <v>90</v>
       </c>
       <c r="G15">
         <v>0.35</v>
@@ -2161,11 +2182,11 @@
       <c r="L15" t="s">
         <v>52</v>
       </c>
-      <c r="M15" s="3">
+      <c r="M15" s="5">
         <v>2</v>
       </c>
-      <c r="N15" s="4" t="s">
-        <v>96</v>
+      <c r="N15" s="6" t="s">
+        <v>100</v>
       </c>
       <c r="O15" t="s">
         <v>63</v>
@@ -2173,22 +2194,22 @@
     </row>
     <row r="16" ht="14.25" customHeight="1" spans="1:15">
       <c r="A16" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B16" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C16" t="s">
         <v>46</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="2">
         <v>3</v>
       </c>
       <c r="E16" t="s">
         <v>47</v>
       </c>
-      <c r="F16" s="2" t="s">
-        <v>86</v>
+      <c r="F16" s="4" t="s">
+        <v>90</v>
       </c>
       <c r="G16">
         <v>0.35</v>
@@ -2208,11 +2229,11 @@
       <c r="L16" t="s">
         <v>52</v>
       </c>
-      <c r="M16" s="3" t="s">
+      <c r="M16" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="N16" s="4" t="s">
-        <v>99</v>
+      <c r="N16" s="6" t="s">
+        <v>103</v>
       </c>
       <c r="O16" t="s">
         <v>63</v>
@@ -2220,22 +2241,22 @@
     </row>
     <row r="17" ht="14.25" customHeight="1" spans="1:15">
       <c r="A17" t="s">
-        <v>100</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>101</v>
+        <v>104</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>105</v>
       </c>
       <c r="C17" t="s">
         <v>57</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="2">
         <v>3</v>
       </c>
       <c r="E17" t="s">
         <v>58</v>
       </c>
-      <c r="F17" s="2" t="s">
-        <v>86</v>
+      <c r="F17" s="4" t="s">
+        <v>90</v>
       </c>
       <c r="G17" t="s">
         <v>53</v>
@@ -2255,11 +2276,11 @@
       <c r="L17" t="s">
         <v>61</v>
       </c>
-      <c r="M17" s="3">
+      <c r="M17" s="5">
         <v>4</v>
       </c>
-      <c r="N17" s="4" t="s">
-        <v>102</v>
+      <c r="N17" s="6" t="s">
+        <v>106</v>
       </c>
       <c r="O17" t="s">
         <v>63</v>
@@ -2267,22 +2288,22 @@
     </row>
     <row r="18" ht="14.25" customHeight="1" spans="1:15">
       <c r="A18" t="s">
-        <v>103</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>104</v>
+        <v>107</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>108</v>
       </c>
       <c r="C18" t="s">
         <v>65</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="2">
         <v>3</v>
       </c>
       <c r="E18" t="s">
         <v>66</v>
       </c>
-      <c r="F18" s="2" t="s">
-        <v>86</v>
+      <c r="F18" s="4" t="s">
+        <v>90</v>
       </c>
       <c r="G18" t="s">
         <v>67</v>
@@ -2302,11 +2323,11 @@
       <c r="L18" t="s">
         <v>61</v>
       </c>
-      <c r="M18" s="3">
+      <c r="M18" s="5">
         <v>3</v>
       </c>
-      <c r="N18" s="4" t="s">
-        <v>105</v>
+      <c r="N18" s="6" t="s">
+        <v>109</v>
       </c>
       <c r="O18" t="s">
         <v>63</v>
@@ -2314,22 +2335,22 @@
     </row>
     <row r="19" ht="14.25" customHeight="1" spans="1:15">
       <c r="A19" t="s">
-        <v>106</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>107</v>
+        <v>110</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>111</v>
       </c>
       <c r="C19" t="s">
         <v>71</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="2">
         <v>3</v>
       </c>
       <c r="E19" t="s">
         <v>66</v>
       </c>
-      <c r="F19" s="2" t="s">
-        <v>86</v>
+      <c r="F19" s="4" t="s">
+        <v>90</v>
       </c>
       <c r="G19">
         <v>0.35</v>
@@ -2349,11 +2370,11 @@
       <c r="L19" t="s">
         <v>52</v>
       </c>
-      <c r="M19" s="3">
+      <c r="M19" s="5">
         <v>2</v>
       </c>
-      <c r="N19" s="4" t="s">
-        <v>108</v>
+      <c r="N19" s="6" t="s">
+        <v>112</v>
       </c>
       <c r="O19" t="s">
         <v>63</v>
@@ -2361,22 +2382,22 @@
     </row>
     <row r="20" spans="1:15">
       <c r="A20" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B20" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C20" t="s">
         <v>46</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="2">
         <v>4</v>
       </c>
       <c r="E20" t="s">
         <v>47</v>
       </c>
-      <c r="F20" s="2" t="s">
-        <v>111</v>
+      <c r="F20" s="4" t="s">
+        <v>115</v>
       </c>
       <c r="G20" t="s">
         <v>49</v>
@@ -2391,16 +2412,16 @@
         <v>50</v>
       </c>
       <c r="K20" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="L20" t="s">
         <v>52</v>
       </c>
-      <c r="M20" s="3">
+      <c r="M20" s="5">
         <v>1</v>
       </c>
-      <c r="N20" s="5" t="s">
-        <v>113</v>
+      <c r="N20" s="7" t="s">
+        <v>117</v>
       </c>
       <c r="O20" t="s">
         <v>63</v>
@@ -2408,22 +2429,22 @@
     </row>
     <row r="21" ht="14.25" customHeight="1" spans="1:15">
       <c r="A21" t="s">
-        <v>114</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>115</v>
+        <v>118</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>119</v>
       </c>
       <c r="C21" t="s">
         <v>65</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="2">
         <v>4</v>
       </c>
       <c r="E21" t="s">
         <v>66</v>
       </c>
-      <c r="F21" s="2" t="s">
-        <v>111</v>
+      <c r="F21" s="4" t="s">
+        <v>115</v>
       </c>
       <c r="G21" t="s">
         <v>67</v>
@@ -2443,245 +2464,245 @@
       <c r="L21" t="s">
         <v>61</v>
       </c>
-      <c r="M21" s="3">
+      <c r="M21" s="5">
         <v>2</v>
       </c>
-      <c r="N21" s="5" t="s">
-        <v>116</v>
+      <c r="N21" s="7" t="s">
+        <v>120</v>
       </c>
       <c r="O21" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="22" ht="14.25" customHeight="1" spans="1:15">
-      <c r="A22" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>118</v>
+      <c r="A22" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>122</v>
       </c>
       <c r="C22" t="s">
         <v>46</v>
       </c>
-      <c r="D22" s="6">
+      <c r="D22" s="9">
         <v>1</v>
       </c>
-      <c r="E22" s="6" t="s">
+      <c r="E22" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="F22" s="6" t="s">
+      <c r="F22" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="G22" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="I22" s="6" t="s">
+      <c r="G22" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="I22" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="J22" s="6" t="s">
+      <c r="J22" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="K22" s="6" t="s">
+      <c r="K22" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="L22" s="6" t="s">
+      <c r="L22" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="M22" s="7" t="s">
+      <c r="M22" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="N22" s="8" t="s">
-        <v>119</v>
+      <c r="N22" s="11" t="s">
+        <v>123</v>
       </c>
       <c r="O22" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="23" ht="14.25" customHeight="1" spans="1:15">
-      <c r="A23" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>121</v>
+      <c r="A23" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>125</v>
       </c>
       <c r="C23" t="s">
         <v>65</v>
       </c>
-      <c r="D23" s="6">
+      <c r="D23" s="9">
         <v>1</v>
       </c>
-      <c r="E23" s="6" t="s">
+      <c r="E23" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="F23" s="6" t="s">
+      <c r="F23" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="G23" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="H23" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="I23" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="J23" s="6" t="s">
+      <c r="G23" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="I23" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="J23" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="K23" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="L23" s="6" t="s">
+      <c r="K23" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="L23" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="M23" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="N23" s="8" t="s">
-        <v>125</v>
+      <c r="M23" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="N23" s="11" t="s">
+        <v>129</v>
       </c>
       <c r="O23" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="24" ht="14.25" customHeight="1" spans="1:15">
-      <c r="A24" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>127</v>
+      <c r="A24" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>131</v>
       </c>
       <c r="C24" t="s">
         <v>57</v>
       </c>
-      <c r="D24" s="6">
+      <c r="D24" s="9">
         <v>1</v>
       </c>
-      <c r="E24" s="6" t="s">
+      <c r="E24" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="F24" s="6" t="s">
+      <c r="F24" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="G24" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="I24" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="J24" s="6" t="s">
+      <c r="G24" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="I24" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="J24" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="K24" s="6" t="s">
+      <c r="K24" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="L24" s="6" t="s">
+      <c r="L24" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="M24" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="N24" s="8" t="s">
-        <v>131</v>
+      <c r="M24" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="N24" s="11" t="s">
+        <v>135</v>
       </c>
       <c r="O24" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="25" ht="14.25" customHeight="1" spans="1:15">
-      <c r="A25" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>133</v>
+      <c r="A25" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>137</v>
       </c>
       <c r="C25" t="s">
         <v>65</v>
       </c>
-      <c r="D25" s="6">
+      <c r="D25" s="9">
         <v>1</v>
       </c>
-      <c r="E25" s="6" t="s">
+      <c r="E25" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="F25" s="6" t="s">
+      <c r="F25" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="G25" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="H25" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="I25" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="J25" s="6" t="s">
+      <c r="G25" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="I25" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="J25" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="K25" s="6" t="s">
+      <c r="K25" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="L25" s="6" t="s">
+      <c r="L25" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="M25" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="N25" s="8" t="s">
-        <v>137</v>
+      <c r="M25" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="N25" s="11" t="s">
+        <v>141</v>
       </c>
       <c r="O25" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="26" spans="1:15">
-      <c r="A26" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>139</v>
+      <c r="A26" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>143</v>
       </c>
       <c r="C26" t="s">
         <v>46</v>
       </c>
-      <c r="D26" s="6">
+      <c r="D26" s="9">
         <v>1</v>
       </c>
-      <c r="E26" s="6" t="s">
+      <c r="E26" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="F26" s="6" t="s">
+      <c r="F26" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="G26" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="I26" s="6" t="s">
+      <c r="G26" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="H26" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="I26" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="J26" s="6" t="s">
+      <c r="J26" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="K26" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="L26" s="6" t="s">
+      <c r="K26" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="L26" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="M26" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="N26" s="6" t="s">
+      <c r="M26" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="N26" s="8" t="s">
         <v>63</v>
       </c>
       <c r="O26" t="s">

--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/制造_职业配置表_Manufacture_ClassConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/制造_职业配置表_Manufacture_ClassConfig.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Work\Cursor\Gravedigger2026\Gravedigger2026\Gravedigger2026\Assets\ConfigTables\Mode2\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\CursorGame_Git\Gravedigger2026\Gravedigger2026\Assets\ConfigTables\Mode2\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="121">
   <si>
     <t>职业ID</t>
   </si>
@@ -395,81 +395,6 @@
   </si>
   <si>
     <t>App_5_51</t>
-  </si>
-  <si>
-    <t>Class_Knight</t>
-  </si>
-  <si>
-    <t>骑士</t>
-  </si>
-  <si>
-    <t>App_05</t>
-  </si>
-  <si>
-    <t>Class_Priest</t>
-  </si>
-  <si>
-    <t>牧师</t>
-  </si>
-  <si>
-    <t>1.2</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>App_09</t>
-  </si>
-  <si>
-    <t>Class_Ranger</t>
-  </si>
-  <si>
-    <t>游侠</t>
-  </si>
-  <si>
-    <t>1.1</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>App_03</t>
-  </si>
-  <si>
-    <t>Class_Warlock</t>
-  </si>
-  <si>
-    <t>术士</t>
-  </si>
-  <si>
-    <t>0.9</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>App_08</t>
-  </si>
-  <si>
-    <t>Class_Servants</t>
-  </si>
-  <si>
-    <t>仆从</t>
-  </si>
-  <si>
-    <t>2.5</t>
-  </si>
-  <si>
-    <t>11</t>
   </si>
 </sst>
 </file>
@@ -642,7 +567,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -658,12 +583,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -984,7 +903,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
@@ -1008,16 +927,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="6">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
@@ -1026,89 +945,89 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="35" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1125,14 +1044,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1479,12 +1390,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:O21"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="3" max="3" width="9.5" customWidth="1"/>
     <col min="4" max="4" width="15.5" style="2" customWidth="1"/>
+    <col min="6" max="6" width="30.6363636363636" customWidth="1"/>
+    <col min="7" max="7" width="21.5454545454545" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
@@ -2471,241 +2384,6 @@
         <v>120</v>
       </c>
       <c r="O21" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="22" ht="14.25" customHeight="1" spans="1:15">
-      <c r="A22" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="C22" t="s">
-        <v>46</v>
-      </c>
-      <c r="D22" s="9">
-        <v>1</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="F22" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="G22" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="H22" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="I22" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="J22" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="K22" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="L22" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="M22" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="N22" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="O22" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="23" ht="14.25" customHeight="1" spans="1:15">
-      <c r="A23" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="C23" t="s">
-        <v>65</v>
-      </c>
-      <c r="D23" s="9">
-        <v>1</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="G23" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="H23" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="I23" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="J23" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="K23" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="L23" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="M23" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="N23" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="O23" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="24" ht="14.25" customHeight="1" spans="1:15">
-      <c r="A24" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="C24" t="s">
-        <v>57</v>
-      </c>
-      <c r="D24" s="9">
-        <v>1</v>
-      </c>
-      <c r="E24" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="F24" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="G24" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="H24" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="I24" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="J24" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="K24" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="L24" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="M24" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="N24" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="O24" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="25" ht="14.25" customHeight="1" spans="1:15">
-      <c r="A25" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="C25" t="s">
-        <v>65</v>
-      </c>
-      <c r="D25" s="9">
-        <v>1</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="G25" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="H25" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="I25" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="J25" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="K25" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="L25" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="M25" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="N25" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="O25" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15">
-      <c r="A26" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="C26" t="s">
-        <v>46</v>
-      </c>
-      <c r="D26" s="9">
-        <v>1</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="F26" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="G26" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="H26" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="I26" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="J26" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="K26" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="L26" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="M26" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="N26" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="O26" t="s">
         <v>63</v>
       </c>
     </row>

--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/制造_职业配置表_Manufacture_ClassConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/制造_职业配置表_Manufacture_ClassConfig.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\CursorGame_Git\Gravedigger2026\Gravedigger2026\Assets\ConfigTables\Mode2\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Work\Cursor\Gravedigger2026\Gravedigger2026\Gravedigger2026\Assets\ConfigTables\Mode2\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="135">
   <si>
     <t>职业ID</t>
   </si>
@@ -43,6 +43,9 @@
     <t>基础职业</t>
   </si>
   <si>
+    <t>转职职业</t>
+  </si>
+  <si>
     <t>等级</t>
   </si>
   <si>
@@ -85,7 +88,10 @@
     <t>参与 WarriorName；外观 ClassAffinity 匹配键</t>
   </si>
   <si>
-    <t>CSV 中文：战士|射手|法师|盗贼 → 枚举；空/非法→Unspecified；预留后续魔法书等条件；不参与命名/外观/PrimaryStat/战斗；不烘进实例</t>
+    <t>CSV 中文：战士|射手|法师|刺客 → 枚举；空/非法→Unspecified；预留后续魔法书等条件；不参与命名/外观/PrimaryStat/战斗；不烘进实例</t>
+  </si>
+  <si>
+    <t>可选文字；空=无转职目标；本轮仅填表，不驱动玩法</t>
   </si>
   <si>
     <t>≥0；仅 UI 展示（UI-016 士兵卡职业名下 Lv.{ClassLevel}）；不参与战斗/制造公式；缺/空 → 0</t>
@@ -133,6 +139,9 @@
     <t>BaseClass</t>
   </si>
   <si>
+    <t>PromoteClass</t>
+  </si>
+  <si>
     <t>ClassLevel</t>
   </si>
   <si>
@@ -169,7 +178,10 @@
     <t>DefaultSkillIds</t>
   </si>
   <si>
-    <t>Class_Warrior_0</t>
+    <t>Class_BaseWarrior</t>
+  </si>
+  <si>
+    <t>枯骨战士</t>
   </si>
   <si>
     <t>战士</t>
@@ -199,193 +211,223 @@
     <t>App_0_00</t>
   </si>
   <si>
+    <t>Class_BaseArcher</t>
+  </si>
+  <si>
+    <t>枯骨射手</t>
+  </si>
+  <si>
+    <t>射手</t>
+  </si>
+  <si>
+    <t>Agility</t>
+  </si>
+  <si>
+    <t>NormalAttackPrimaryMult_15|AttackSpeedBase_0.5|AttackSpeedAgiDiv_60|30_30|0.1_0.1</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>Ranged</t>
+  </si>
+  <si>
+    <t>App_0_10</t>
+  </si>
+  <si>
+    <t>Class_BaseMage</t>
+  </si>
+  <si>
+    <t>枯骨法师</t>
+  </si>
+  <si>
+    <t>法师</t>
+  </si>
+  <si>
+    <t>Intelligence</t>
+  </si>
+  <si>
+    <t>0.8</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>App_0_20</t>
+  </si>
+  <si>
+    <t>Class_BaseRogue</t>
+  </si>
+  <si>
+    <t>枯骨刺客</t>
+  </si>
+  <si>
+    <t>刺客</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>App_0_30</t>
+  </si>
+  <si>
+    <t>Class_Warrior</t>
+  </si>
+  <si>
+    <t>NormalAttackPrimaryMult_30|AttackSpeedBase_0.5|AttackSpeedAgiDiv_60|30_30|0.1_0.1</t>
+  </si>
+  <si>
+    <t>0.3</t>
+  </si>
+  <si>
+    <t>App_0_01</t>
+  </si>
+  <si>
     <t>Skill_01</t>
   </si>
   <si>
-    <t>Class_Archer_0</t>
-  </si>
-  <si>
-    <t>射手</t>
-  </si>
-  <si>
-    <t>Agility</t>
-  </si>
-  <si>
-    <t>NormalAttackPrimaryMult_15|AttackSpeedBase_0.5|AttackSpeedAgiDiv_60|30_30|0.1_0.1</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>Ranged</t>
-  </si>
-  <si>
-    <t>App_0_10</t>
+    <t>Class_Archer</t>
+  </si>
+  <si>
+    <t>App_0_11</t>
+  </si>
+  <si>
+    <t>Skill_02</t>
+  </si>
+  <si>
+    <t>Class_Mage</t>
+  </si>
+  <si>
+    <t>App_0_21</t>
+  </si>
+  <si>
+    <t>Skill_03</t>
+  </si>
+  <si>
+    <t>Class_Rogue</t>
+  </si>
+  <si>
+    <t>App_0_31</t>
+  </si>
+  <si>
+    <t>Skill_04</t>
+  </si>
+  <si>
+    <t>Class_Guardian</t>
+  </si>
+  <si>
+    <t>近卫</t>
+  </si>
+  <si>
+    <t>NormalAttackPrimaryMult_45|AttackSpeedBase_0.5|AttackSpeedAgiDiv_60|30_30|0.1_0.1</t>
+  </si>
+  <si>
+    <t>App_0_02</t>
+  </si>
+  <si>
+    <t>Skill_05</t>
+  </si>
+  <si>
+    <t>Class_BombMaster</t>
+  </si>
+  <si>
+    <t>炸弹师</t>
+  </si>
+  <si>
+    <t>App_0_12</t>
+  </si>
+  <si>
+    <t>Skill_06</t>
+  </si>
+  <si>
+    <t>Class_IceMage</t>
+  </si>
+  <si>
+    <t>冰法</t>
+  </si>
+  <si>
+    <t>App_0_22</t>
+  </si>
+  <si>
+    <t>Skill_07</t>
+  </si>
+  <si>
+    <t>Class_Brawler</t>
+  </si>
+  <si>
+    <t>格斗师</t>
+  </si>
+  <si>
+    <t>App_0_32</t>
+  </si>
+  <si>
+    <t>Skill_08</t>
+  </si>
+  <si>
+    <t>Class_Berserker</t>
+  </si>
+  <si>
+    <t>狂战士</t>
+  </si>
+  <si>
+    <t>App_0_03</t>
+  </si>
+  <si>
+    <t>Skill_09</t>
+  </si>
+  <si>
+    <t>Class_Longbowman</t>
+  </si>
+  <si>
+    <t>长弓手</t>
+  </si>
+  <si>
+    <t>App_0_13</t>
+  </si>
+  <si>
+    <t>Skill_10</t>
+  </si>
+  <si>
+    <t>Class_FireMage</t>
+  </si>
+  <si>
+    <t>火法</t>
+  </si>
+  <si>
+    <t>App_0_23</t>
+  </si>
+  <si>
+    <t>Skill_11</t>
+  </si>
+  <si>
+    <t>Class_Shadowblade</t>
+  </si>
+  <si>
+    <t>影刃</t>
+  </si>
+  <si>
+    <t>App_0_33</t>
+  </si>
+  <si>
+    <t>Skill_12</t>
+  </si>
+  <si>
+    <t>Class_Paladin</t>
+  </si>
+  <si>
+    <t>圣骑士</t>
+  </si>
+  <si>
+    <t>NormalAttackPrimaryMult_60|AttackSpeedBase_0.5|AttackSpeedAgiDiv_60|30_30|0.1_0.1</t>
+  </si>
+  <si>
+    <t>1.5</t>
+  </si>
+  <si>
+    <t>App_4_41</t>
   </si>
   <si>
     <t/>
-  </si>
-  <si>
-    <t>Class_Mage_0</t>
-  </si>
-  <si>
-    <t>法师</t>
-  </si>
-  <si>
-    <t>Intelligence</t>
-  </si>
-  <si>
-    <t>0.8</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>App_0_20</t>
-  </si>
-  <si>
-    <t>Class_Rogue_0</t>
-  </si>
-  <si>
-    <t>盗贼</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>App_0_30</t>
-  </si>
-  <si>
-    <t>Class_Warrior</t>
-  </si>
-  <si>
-    <t>战士2</t>
-  </si>
-  <si>
-    <t>NormalAttackPrimaryMult_30|AttackSpeedBase_0.5|AttackSpeedAgiDiv_60|30_30|0.1_0.1</t>
-  </si>
-  <si>
-    <t>0.3</t>
-  </si>
-  <si>
-    <t>App_0_01</t>
-  </si>
-  <si>
-    <t>Class_Archer</t>
-  </si>
-  <si>
-    <t>射手2</t>
-  </si>
-  <si>
-    <t>App_0_11</t>
-  </si>
-  <si>
-    <t>Class_Mage</t>
-  </si>
-  <si>
-    <t>法师2</t>
-  </si>
-  <si>
-    <t>App_0_21</t>
-  </si>
-  <si>
-    <t>Class_Rogue</t>
-  </si>
-  <si>
-    <t>盗贼2</t>
-  </si>
-  <si>
-    <t>App_0_31</t>
-  </si>
-  <si>
-    <t>Class_Guardian</t>
-  </si>
-  <si>
-    <t>近卫</t>
-  </si>
-  <si>
-    <t>NormalAttackPrimaryMult_45|AttackSpeedBase_0.5|AttackSpeedAgiDiv_60|30_30|0.1_0.1</t>
-  </si>
-  <si>
-    <t>App_0_02</t>
-  </si>
-  <si>
-    <t>Class_BombMaster</t>
-  </si>
-  <si>
-    <t>炸弹师</t>
-  </si>
-  <si>
-    <t>App_0_12</t>
-  </si>
-  <si>
-    <t>Class_IceMage</t>
-  </si>
-  <si>
-    <t>冰法</t>
-  </si>
-  <si>
-    <t>App_0_22</t>
-  </si>
-  <si>
-    <t>Class_Brawler</t>
-  </si>
-  <si>
-    <t>格斗师</t>
-  </si>
-  <si>
-    <t>App_0_32</t>
-  </si>
-  <si>
-    <t>Class_Berserker</t>
-  </si>
-  <si>
-    <t>狂战士</t>
-  </si>
-  <si>
-    <t>App_0_03</t>
-  </si>
-  <si>
-    <t>Class_Longbowman</t>
-  </si>
-  <si>
-    <t>长弓手</t>
-  </si>
-  <si>
-    <t>App_0_13</t>
-  </si>
-  <si>
-    <t>Class_FireMage</t>
-  </si>
-  <si>
-    <t>火法</t>
-  </si>
-  <si>
-    <t>App_0_23</t>
-  </si>
-  <si>
-    <t>Class_Shadowblade</t>
-  </si>
-  <si>
-    <t>影刃</t>
-  </si>
-  <si>
-    <t>App_0_33</t>
-  </si>
-  <si>
-    <t>Class_Paladin</t>
-  </si>
-  <si>
-    <t>圣骑士</t>
-  </si>
-  <si>
-    <t>NormalAttackPrimaryMult_60|AttackSpeedBase_0.5|AttackSpeedAgiDiv_60|30_30|0.1_0.1</t>
-  </si>
-  <si>
-    <t>1.5</t>
-  </si>
-  <si>
-    <t>App_4_41</t>
   </si>
   <si>
     <t>Class_DarkMage</t>
@@ -1390,17 +1432,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <dimension ref="A1:P21"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="3" max="3" width="9.5" customWidth="1"/>
     <col min="4" max="4" width="15.5" style="2" customWidth="1"/>
-    <col min="6" max="6" width="30.6363636363636" customWidth="1"/>
-    <col min="7" max="7" width="21.5454545454545" customWidth="1"/>
+    <col min="6" max="6" width="30.6333333333333" customWidth="1"/>
+    <col min="7" max="7" width="21.5416666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:16">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1410,10 +1452,10 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
@@ -1446,945 +1488,975 @@
       <c r="O1" t="s">
         <v>14</v>
       </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:16">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E2" t="s">
+      <c r="D2" t="s">
         <v>19</v>
       </c>
+      <c r="E2" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="F2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O2" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="P2" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:15">
+    <row r="3" s="1" customFormat="1" spans="1:16">
       <c r="A3" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E3" s="1" t="s">
         <v>34</v>
       </c>
+      <c r="D3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="F3" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
-    <row r="4" ht="14.25" customHeight="1" spans="1:15">
+    <row r="4" ht="14.25" customHeight="1" spans="1:16">
       <c r="A4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B4" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D4" s="2">
+        <v>50</v>
+      </c>
+      <c r="E4" s="2">
         <v>1</v>
       </c>
-      <c r="E4" t="s">
-        <v>47</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="G4">
+      <c r="F4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H4">
         <v>0.35</v>
       </c>
-      <c r="H4" t="s">
-        <v>49</v>
-      </c>
       <c r="I4" t="s">
+        <v>53</v>
+      </c>
+      <c r="J4" t="s">
+        <v>54</v>
+      </c>
+      <c r="K4" t="s">
+        <v>54</v>
+      </c>
+      <c r="L4" t="s">
+        <v>55</v>
+      </c>
+      <c r="M4" t="s">
+        <v>56</v>
+      </c>
+      <c r="N4" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="O4" s="6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" ht="14.25" customHeight="1" spans="1:16">
+      <c r="A5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E5" s="2">
+        <v>1</v>
+      </c>
+      <c r="F5" t="s">
+        <v>62</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="H5" t="s">
+        <v>57</v>
+      </c>
+      <c r="I5" t="s">
+        <v>53</v>
+      </c>
+      <c r="J5" t="s">
+        <v>64</v>
+      </c>
+      <c r="K5" t="s">
+        <v>57</v>
+      </c>
+      <c r="L5" t="s">
+        <v>53</v>
+      </c>
+      <c r="M5" t="s">
+        <v>65</v>
+      </c>
+      <c r="N5" s="5">
+        <v>4</v>
+      </c>
+      <c r="O5" s="6" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" ht="14.25" customHeight="1" spans="1:16">
+      <c r="A6" t="s">
+        <v>67</v>
+      </c>
+      <c r="B6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E6" s="2">
+        <v>1</v>
+      </c>
+      <c r="F6" t="s">
+        <v>70</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="H6" t="s">
+        <v>71</v>
+      </c>
+      <c r="I6" t="s">
+        <v>53</v>
+      </c>
+      <c r="J6" t="s">
+        <v>72</v>
+      </c>
+      <c r="K6" t="s">
+        <v>57</v>
+      </c>
+      <c r="L6" t="s">
+        <v>53</v>
+      </c>
+      <c r="M6" t="s">
+        <v>65</v>
+      </c>
+      <c r="N6" s="5">
+        <v>3</v>
+      </c>
+      <c r="O6" s="6" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="7" ht="14.25" customHeight="1" spans="1:16">
+      <c r="A7" t="s">
+        <v>74</v>
+      </c>
+      <c r="B7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" t="s">
+        <v>76</v>
+      </c>
+      <c r="E7" s="2">
+        <v>1</v>
+      </c>
+      <c r="F7" t="s">
+        <v>62</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="H7">
+        <v>0.35</v>
+      </c>
+      <c r="I7" t="s">
+        <v>53</v>
+      </c>
+      <c r="J7" t="s">
+        <v>54</v>
+      </c>
+      <c r="K7" t="s">
+        <v>54</v>
+      </c>
+      <c r="L7" t="s">
+        <v>77</v>
+      </c>
+      <c r="M7" t="s">
+        <v>56</v>
+      </c>
+      <c r="N7" s="5">
+        <v>2</v>
+      </c>
+      <c r="O7" s="6" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8" ht="14.25" customHeight="1" spans="1:16">
+      <c r="A8" t="s">
+        <v>79</v>
+      </c>
+      <c r="B8" t="s">
         <v>50</v>
       </c>
-      <c r="J4" t="s">
+      <c r="C8" t="s">
         <v>50</v>
       </c>
-      <c r="K4" t="s">
+      <c r="E8" s="2">
+        <v>2</v>
+      </c>
+      <c r="F8" t="s">
         <v>51</v>
       </c>
-      <c r="L4" t="s">
-        <v>52</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="N4" s="6" t="s">
+      <c r="G8" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="H8" t="s">
+        <v>81</v>
+      </c>
+      <c r="I8" t="s">
+        <v>53</v>
+      </c>
+      <c r="J8" t="s">
         <v>54</v>
       </c>
-      <c r="O4" t="s">
+      <c r="K8" t="s">
+        <v>54</v>
+      </c>
+      <c r="L8" t="s">
         <v>55</v>
       </c>
+      <c r="M8" t="s">
+        <v>56</v>
+      </c>
+      <c r="N8" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="O8" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="P8" t="s">
+        <v>83</v>
+      </c>
     </row>
-    <row r="5" ht="14.25" customHeight="1" spans="1:15">
-      <c r="A5" t="s">
+    <row r="9" ht="14.25" customHeight="1" spans="1:16">
+      <c r="A9" t="s">
+        <v>84</v>
+      </c>
+      <c r="B9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C9" t="s">
+        <v>61</v>
+      </c>
+      <c r="E9" s="2">
+        <v>2</v>
+      </c>
+      <c r="F9" t="s">
+        <v>62</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="H9" t="s">
+        <v>57</v>
+      </c>
+      <c r="I9" t="s">
+        <v>53</v>
+      </c>
+      <c r="J9" t="s">
+        <v>64</v>
+      </c>
+      <c r="K9" t="s">
+        <v>57</v>
+      </c>
+      <c r="L9" t="s">
+        <v>53</v>
+      </c>
+      <c r="M9" t="s">
+        <v>65</v>
+      </c>
+      <c r="N9" s="5">
+        <v>4</v>
+      </c>
+      <c r="O9" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="P9" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="10" ht="14.25" customHeight="1" spans="1:16">
+      <c r="A10" t="s">
+        <v>87</v>
+      </c>
+      <c r="B10" t="s">
+        <v>69</v>
+      </c>
+      <c r="C10" t="s">
+        <v>69</v>
+      </c>
+      <c r="E10" s="2">
+        <v>2</v>
+      </c>
+      <c r="F10" t="s">
+        <v>70</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="H10" t="s">
+        <v>71</v>
+      </c>
+      <c r="I10" t="s">
+        <v>53</v>
+      </c>
+      <c r="J10" t="s">
+        <v>72</v>
+      </c>
+      <c r="K10" t="s">
+        <v>57</v>
+      </c>
+      <c r="L10" t="s">
+        <v>53</v>
+      </c>
+      <c r="M10" t="s">
+        <v>65</v>
+      </c>
+      <c r="N10" s="5">
+        <v>3</v>
+      </c>
+      <c r="O10" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="P10" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="11" ht="14.25" customHeight="1" spans="1:16">
+      <c r="A11" t="s">
+        <v>90</v>
+      </c>
+      <c r="B11" t="s">
+        <v>76</v>
+      </c>
+      <c r="C11" t="s">
+        <v>76</v>
+      </c>
+      <c r="D11" t="s">
+        <v>76</v>
+      </c>
+      <c r="E11" s="2">
+        <v>2</v>
+      </c>
+      <c r="F11" t="s">
+        <v>62</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="H11">
+        <v>0.35</v>
+      </c>
+      <c r="I11" t="s">
+        <v>53</v>
+      </c>
+      <c r="J11" t="s">
+        <v>54</v>
+      </c>
+      <c r="K11" t="s">
+        <v>54</v>
+      </c>
+      <c r="L11" t="s">
+        <v>77</v>
+      </c>
+      <c r="M11" t="s">
         <v>56</v>
       </c>
-      <c r="B5" t="s">
+      <c r="N11" s="5">
+        <v>2</v>
+      </c>
+      <c r="O11" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="P11" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="12" ht="14.25" customHeight="1" spans="1:16">
+      <c r="A12" t="s">
+        <v>93</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C12" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="E12" s="2">
+        <v>3</v>
+      </c>
+      <c r="F12" t="s">
+        <v>51</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="H12">
+        <v>0.35</v>
+      </c>
+      <c r="I12" t="s">
+        <v>53</v>
+      </c>
+      <c r="J12" t="s">
+        <v>54</v>
+      </c>
+      <c r="K12" t="s">
+        <v>54</v>
+      </c>
+      <c r="L12" t="s">
+        <v>55</v>
+      </c>
+      <c r="M12" t="s">
+        <v>56</v>
+      </c>
+      <c r="N12" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C5" t="s">
+      <c r="O12" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="P12" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="13" ht="14.25" customHeight="1" spans="1:16">
+      <c r="A13" t="s">
+        <v>98</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="C13" t="s">
+        <v>61</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="E13" s="2">
+        <v>3</v>
+      </c>
+      <c r="F13" t="s">
+        <v>62</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="H13" t="s">
         <v>57</v>
       </c>
-      <c r="D5" s="2">
+      <c r="I13" t="s">
+        <v>53</v>
+      </c>
+      <c r="J13" t="s">
+        <v>64</v>
+      </c>
+      <c r="K13" t="s">
+        <v>57</v>
+      </c>
+      <c r="L13" t="s">
+        <v>53</v>
+      </c>
+      <c r="M13" t="s">
+        <v>65</v>
+      </c>
+      <c r="N13" s="5">
+        <v>4</v>
+      </c>
+      <c r="O13" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="P13" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="14" ht="14.25" customHeight="1" spans="1:16">
+      <c r="A14" t="s">
+        <v>102</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="C14" t="s">
+        <v>69</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="E14" s="2">
+        <v>3</v>
+      </c>
+      <c r="F14" t="s">
+        <v>70</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="H14" t="s">
+        <v>71</v>
+      </c>
+      <c r="I14" t="s">
+        <v>53</v>
+      </c>
+      <c r="J14" t="s">
+        <v>72</v>
+      </c>
+      <c r="K14" t="s">
+        <v>57</v>
+      </c>
+      <c r="L14" t="s">
+        <v>53</v>
+      </c>
+      <c r="M14" t="s">
+        <v>65</v>
+      </c>
+      <c r="N14" s="5">
+        <v>3</v>
+      </c>
+      <c r="O14" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="P14" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="15" ht="14.25" customHeight="1" spans="1:16">
+      <c r="A15" t="s">
+        <v>106</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="C15" t="s">
+        <v>76</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="E15" s="2">
+        <v>3</v>
+      </c>
+      <c r="F15" t="s">
+        <v>51</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="H15">
+        <v>0.35</v>
+      </c>
+      <c r="I15" t="s">
+        <v>53</v>
+      </c>
+      <c r="J15" t="s">
+        <v>54</v>
+      </c>
+      <c r="K15" t="s">
+        <v>54</v>
+      </c>
+      <c r="L15" t="s">
+        <v>55</v>
+      </c>
+      <c r="M15" t="s">
+        <v>56</v>
+      </c>
+      <c r="N15" s="5">
+        <v>2</v>
+      </c>
+      <c r="O15" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="P15" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="16" ht="14.25" customHeight="1" spans="1:16">
+      <c r="A16" t="s">
+        <v>110</v>
+      </c>
+      <c r="B16" t="s">
+        <v>111</v>
+      </c>
+      <c r="C16" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16" t="s">
+        <v>111</v>
+      </c>
+      <c r="E16" s="2">
+        <v>3</v>
+      </c>
+      <c r="F16" t="s">
+        <v>51</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="H16">
+        <v>0.35</v>
+      </c>
+      <c r="I16" t="s">
+        <v>53</v>
+      </c>
+      <c r="J16" t="s">
+        <v>54</v>
+      </c>
+      <c r="K16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N16" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="O16" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="P16" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="17" ht="14.25" customHeight="1" spans="1:16">
+      <c r="A17" t="s">
+        <v>114</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="C17" t="s">
+        <v>61</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="E17" s="2">
+        <v>3</v>
+      </c>
+      <c r="F17" t="s">
+        <v>62</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="H17" t="s">
+        <v>57</v>
+      </c>
+      <c r="I17" t="s">
+        <v>53</v>
+      </c>
+      <c r="J17" t="s">
+        <v>64</v>
+      </c>
+      <c r="K17" t="s">
+        <v>57</v>
+      </c>
+      <c r="L17" t="s">
+        <v>53</v>
+      </c>
+      <c r="M17" t="s">
+        <v>65</v>
+      </c>
+      <c r="N17" s="5">
+        <v>4</v>
+      </c>
+      <c r="O17" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="P17" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="18" ht="14.25" customHeight="1" spans="1:16">
+      <c r="A18" t="s">
+        <v>118</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C18" t="s">
+        <v>69</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="E18" s="2">
+        <v>3</v>
+      </c>
+      <c r="F18" t="s">
+        <v>70</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="H18" t="s">
+        <v>71</v>
+      </c>
+      <c r="I18" t="s">
+        <v>53</v>
+      </c>
+      <c r="J18" t="s">
+        <v>72</v>
+      </c>
+      <c r="K18" t="s">
+        <v>57</v>
+      </c>
+      <c r="L18" t="s">
+        <v>53</v>
+      </c>
+      <c r="M18" t="s">
+        <v>65</v>
+      </c>
+      <c r="N18" s="5">
+        <v>3</v>
+      </c>
+      <c r="O18" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="P18" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="19" ht="14.25" customHeight="1" spans="1:16">
+      <c r="A19" t="s">
+        <v>122</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C19" t="s">
+        <v>76</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="E19" s="2">
+        <v>3</v>
+      </c>
+      <c r="F19" t="s">
+        <v>70</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="H19">
+        <v>0.35</v>
+      </c>
+      <c r="I19" t="s">
+        <v>53</v>
+      </c>
+      <c r="J19" t="s">
+        <v>54</v>
+      </c>
+      <c r="K19" t="s">
+        <v>54</v>
+      </c>
+      <c r="L19" t="s">
+        <v>55</v>
+      </c>
+      <c r="M19" t="s">
+        <v>56</v>
+      </c>
+      <c r="N19" s="5">
+        <v>2</v>
+      </c>
+      <c r="O19" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="P19" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
+      <c r="A20" t="s">
+        <v>126</v>
+      </c>
+      <c r="B20" t="s">
+        <v>127</v>
+      </c>
+      <c r="C20" t="s">
+        <v>50</v>
+      </c>
+      <c r="D20" t="s">
+        <v>127</v>
+      </c>
+      <c r="E20" s="2">
+        <v>4</v>
+      </c>
+      <c r="F20" t="s">
+        <v>51</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H20" t="s">
+        <v>53</v>
+      </c>
+      <c r="I20" t="s">
+        <v>53</v>
+      </c>
+      <c r="J20" t="s">
+        <v>54</v>
+      </c>
+      <c r="K20" t="s">
+        <v>54</v>
+      </c>
+      <c r="L20" t="s">
+        <v>129</v>
+      </c>
+      <c r="M20" t="s">
+        <v>56</v>
+      </c>
+      <c r="N20" s="5">
         <v>1</v>
       </c>
-      <c r="E5" t="s">
-        <v>58</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="G5" t="s">
-        <v>53</v>
-      </c>
-      <c r="H5" t="s">
-        <v>49</v>
-      </c>
-      <c r="I5" t="s">
-        <v>60</v>
-      </c>
-      <c r="J5" t="s">
-        <v>53</v>
-      </c>
-      <c r="K5" t="s">
-        <v>49</v>
-      </c>
-      <c r="L5" t="s">
-        <v>61</v>
-      </c>
-      <c r="M5" s="5">
+      <c r="O20" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="P20" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="21" ht="14.25" customHeight="1" spans="1:16">
+      <c r="A21" t="s">
+        <v>132</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="C21" t="s">
+        <v>69</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="E21" s="2">
         <v>4</v>
       </c>
-      <c r="N5" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="O5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="6" ht="14.25" customHeight="1" spans="1:15">
-      <c r="A6" t="s">
-        <v>64</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="F21" t="s">
+        <v>70</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H21" t="s">
+        <v>71</v>
+      </c>
+      <c r="I21" t="s">
+        <v>53</v>
+      </c>
+      <c r="J21" t="s">
+        <v>72</v>
+      </c>
+      <c r="K21" t="s">
+        <v>57</v>
+      </c>
+      <c r="L21" t="s">
+        <v>53</v>
+      </c>
+      <c r="M21" t="s">
         <v>65</v>
       </c>
-      <c r="C6" t="s">
-        <v>65</v>
-      </c>
-      <c r="D6" s="2">
-        <v>1</v>
-      </c>
-      <c r="E6" t="s">
-        <v>66</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="G6" t="s">
-        <v>67</v>
-      </c>
-      <c r="H6" t="s">
-        <v>49</v>
-      </c>
-      <c r="I6" t="s">
-        <v>68</v>
-      </c>
-      <c r="J6" t="s">
-        <v>53</v>
-      </c>
-      <c r="K6" t="s">
-        <v>49</v>
-      </c>
-      <c r="L6" t="s">
-        <v>61</v>
-      </c>
-      <c r="M6" s="5">
-        <v>3</v>
-      </c>
-      <c r="N6" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="O6" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="7" ht="14.25" customHeight="1" spans="1:15">
-      <c r="A7" t="s">
-        <v>70</v>
-      </c>
-      <c r="B7" t="s">
-        <v>71</v>
-      </c>
-      <c r="C7" t="s">
-        <v>71</v>
-      </c>
-      <c r="D7" s="2">
-        <v>1</v>
-      </c>
-      <c r="E7" t="s">
-        <v>58</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="G7">
-        <v>0.35</v>
-      </c>
-      <c r="H7" t="s">
-        <v>49</v>
-      </c>
-      <c r="I7" t="s">
-        <v>50</v>
-      </c>
-      <c r="J7" t="s">
-        <v>50</v>
-      </c>
-      <c r="K7" t="s">
-        <v>72</v>
-      </c>
-      <c r="L7" t="s">
-        <v>52</v>
-      </c>
-      <c r="M7" s="5">
+      <c r="N21" s="5">
         <v>2</v>
       </c>
-      <c r="N7" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="O7" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="8" ht="14.25" customHeight="1" spans="1:15">
-      <c r="A8" t="s">
-        <v>74</v>
-      </c>
-      <c r="B8" t="s">
-        <v>75</v>
-      </c>
-      <c r="C8" t="s">
-        <v>46</v>
-      </c>
-      <c r="D8" s="2">
-        <v>2</v>
-      </c>
-      <c r="E8" t="s">
-        <v>47</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="G8" t="s">
-        <v>77</v>
-      </c>
-      <c r="H8" t="s">
-        <v>49</v>
-      </c>
-      <c r="I8" t="s">
-        <v>50</v>
-      </c>
-      <c r="J8" t="s">
-        <v>50</v>
-      </c>
-      <c r="K8" t="s">
-        <v>51</v>
-      </c>
-      <c r="L8" t="s">
-        <v>52</v>
-      </c>
-      <c r="M8" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="N8" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="O8" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="9" ht="14.25" customHeight="1" spans="1:15">
-      <c r="A9" t="s">
-        <v>79</v>
-      </c>
-      <c r="B9" t="s">
-        <v>80</v>
-      </c>
-      <c r="C9" t="s">
-        <v>57</v>
-      </c>
-      <c r="D9" s="2">
-        <v>2</v>
-      </c>
-      <c r="E9" t="s">
-        <v>58</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="G9" t="s">
-        <v>53</v>
-      </c>
-      <c r="H9" t="s">
-        <v>49</v>
-      </c>
-      <c r="I9" t="s">
-        <v>60</v>
-      </c>
-      <c r="J9" t="s">
-        <v>53</v>
-      </c>
-      <c r="K9" t="s">
-        <v>49</v>
-      </c>
-      <c r="L9" t="s">
-        <v>61</v>
-      </c>
-      <c r="M9" s="5">
-        <v>4</v>
-      </c>
-      <c r="N9" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="O9" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="10" ht="14.25" customHeight="1" spans="1:15">
-      <c r="A10" t="s">
-        <v>82</v>
-      </c>
-      <c r="B10" t="s">
-        <v>83</v>
-      </c>
-      <c r="C10" t="s">
-        <v>65</v>
-      </c>
-      <c r="D10" s="2">
-        <v>2</v>
-      </c>
-      <c r="E10" t="s">
-        <v>66</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="G10" t="s">
-        <v>67</v>
-      </c>
-      <c r="H10" t="s">
-        <v>49</v>
-      </c>
-      <c r="I10" t="s">
-        <v>68</v>
-      </c>
-      <c r="J10" t="s">
-        <v>53</v>
-      </c>
-      <c r="K10" t="s">
-        <v>49</v>
-      </c>
-      <c r="L10" t="s">
-        <v>61</v>
-      </c>
-      <c r="M10" s="5">
-        <v>3</v>
-      </c>
-      <c r="N10" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="O10" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="11" ht="14.25" customHeight="1" spans="1:15">
-      <c r="A11" t="s">
-        <v>85</v>
-      </c>
-      <c r="B11" t="s">
-        <v>86</v>
-      </c>
-      <c r="C11" t="s">
-        <v>71</v>
-      </c>
-      <c r="D11" s="2">
-        <v>2</v>
-      </c>
-      <c r="E11" t="s">
-        <v>58</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="G11">
-        <v>0.35</v>
-      </c>
-      <c r="H11" t="s">
-        <v>49</v>
-      </c>
-      <c r="I11" t="s">
-        <v>50</v>
-      </c>
-      <c r="J11" t="s">
-        <v>50</v>
-      </c>
-      <c r="K11" t="s">
-        <v>72</v>
-      </c>
-      <c r="L11" t="s">
-        <v>52</v>
-      </c>
-      <c r="M11" s="5">
-        <v>2</v>
-      </c>
-      <c r="N11" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="O11" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="12" ht="14.25" customHeight="1" spans="1:15">
-      <c r="A12" t="s">
-        <v>88</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C12" t="s">
-        <v>46</v>
-      </c>
-      <c r="D12" s="2">
-        <v>3</v>
-      </c>
-      <c r="E12" t="s">
-        <v>47</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="G12">
-        <v>0.35</v>
-      </c>
-      <c r="H12" t="s">
-        <v>49</v>
-      </c>
-      <c r="I12" t="s">
-        <v>50</v>
-      </c>
-      <c r="J12" t="s">
-        <v>50</v>
-      </c>
-      <c r="K12" t="s">
-        <v>51</v>
-      </c>
-      <c r="L12" t="s">
-        <v>52</v>
-      </c>
-      <c r="M12" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="N12" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="O12" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="13" ht="14.25" customHeight="1" spans="1:15">
-      <c r="A13" t="s">
-        <v>92</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C13" t="s">
-        <v>57</v>
-      </c>
-      <c r="D13" s="2">
-        <v>3</v>
-      </c>
-      <c r="E13" t="s">
-        <v>58</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="G13" t="s">
-        <v>53</v>
-      </c>
-      <c r="H13" t="s">
-        <v>49</v>
-      </c>
-      <c r="I13" t="s">
-        <v>60</v>
-      </c>
-      <c r="J13" t="s">
-        <v>53</v>
-      </c>
-      <c r="K13" t="s">
-        <v>49</v>
-      </c>
-      <c r="L13" t="s">
-        <v>61</v>
-      </c>
-      <c r="M13" s="5">
-        <v>4</v>
-      </c>
-      <c r="N13" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="O13" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="14" ht="14.25" customHeight="1" spans="1:15">
-      <c r="A14" t="s">
-        <v>95</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="C14" t="s">
-        <v>65</v>
-      </c>
-      <c r="D14" s="2">
-        <v>3</v>
-      </c>
-      <c r="E14" t="s">
-        <v>66</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="G14" t="s">
-        <v>67</v>
-      </c>
-      <c r="H14" t="s">
-        <v>49</v>
-      </c>
-      <c r="I14" t="s">
-        <v>68</v>
-      </c>
-      <c r="J14" t="s">
-        <v>53</v>
-      </c>
-      <c r="K14" t="s">
-        <v>49</v>
-      </c>
-      <c r="L14" t="s">
-        <v>61</v>
-      </c>
-      <c r="M14" s="5">
-        <v>3</v>
-      </c>
-      <c r="N14" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="O14" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="15" ht="14.25" customHeight="1" spans="1:15">
-      <c r="A15" t="s">
-        <v>98</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="C15" t="s">
-        <v>71</v>
-      </c>
-      <c r="D15" s="2">
-        <v>3</v>
-      </c>
-      <c r="E15" t="s">
-        <v>47</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="G15">
-        <v>0.35</v>
-      </c>
-      <c r="H15" t="s">
-        <v>49</v>
-      </c>
-      <c r="I15" t="s">
-        <v>50</v>
-      </c>
-      <c r="J15" t="s">
-        <v>50</v>
-      </c>
-      <c r="K15" t="s">
-        <v>51</v>
-      </c>
-      <c r="L15" t="s">
-        <v>52</v>
-      </c>
-      <c r="M15" s="5">
-        <v>2</v>
-      </c>
-      <c r="N15" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="O15" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="16" ht="14.25" customHeight="1" spans="1:15">
-      <c r="A16" t="s">
-        <v>101</v>
-      </c>
-      <c r="B16" t="s">
-        <v>102</v>
-      </c>
-      <c r="C16" t="s">
-        <v>46</v>
-      </c>
-      <c r="D16" s="2">
-        <v>3</v>
-      </c>
-      <c r="E16" t="s">
-        <v>47</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="G16">
-        <v>0.35</v>
-      </c>
-      <c r="H16" t="s">
-        <v>49</v>
-      </c>
-      <c r="I16" t="s">
-        <v>50</v>
-      </c>
-      <c r="J16" t="s">
-        <v>50</v>
-      </c>
-      <c r="K16" t="s">
-        <v>51</v>
-      </c>
-      <c r="L16" t="s">
-        <v>52</v>
-      </c>
-      <c r="M16" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="N16" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="O16" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="17" ht="14.25" customHeight="1" spans="1:15">
-      <c r="A17" t="s">
-        <v>104</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="C17" t="s">
-        <v>57</v>
-      </c>
-      <c r="D17" s="2">
-        <v>3</v>
-      </c>
-      <c r="E17" t="s">
-        <v>58</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="G17" t="s">
-        <v>53</v>
-      </c>
-      <c r="H17" t="s">
-        <v>49</v>
-      </c>
-      <c r="I17" t="s">
-        <v>60</v>
-      </c>
-      <c r="J17" t="s">
-        <v>53</v>
-      </c>
-      <c r="K17" t="s">
-        <v>49</v>
-      </c>
-      <c r="L17" t="s">
-        <v>61</v>
-      </c>
-      <c r="M17" s="5">
-        <v>4</v>
-      </c>
-      <c r="N17" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="O17" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="18" ht="14.25" customHeight="1" spans="1:15">
-      <c r="A18" t="s">
-        <v>107</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="C18" t="s">
-        <v>65</v>
-      </c>
-      <c r="D18" s="2">
-        <v>3</v>
-      </c>
-      <c r="E18" t="s">
-        <v>66</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="G18" t="s">
-        <v>67</v>
-      </c>
-      <c r="H18" t="s">
-        <v>49</v>
-      </c>
-      <c r="I18" t="s">
-        <v>68</v>
-      </c>
-      <c r="J18" t="s">
-        <v>53</v>
-      </c>
-      <c r="K18" t="s">
-        <v>49</v>
-      </c>
-      <c r="L18" t="s">
-        <v>61</v>
-      </c>
-      <c r="M18" s="5">
-        <v>3</v>
-      </c>
-      <c r="N18" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="O18" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="19" ht="14.25" customHeight="1" spans="1:15">
-      <c r="A19" t="s">
-        <v>110</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="C19" t="s">
-        <v>71</v>
-      </c>
-      <c r="D19" s="2">
-        <v>3</v>
-      </c>
-      <c r="E19" t="s">
-        <v>66</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="G19">
-        <v>0.35</v>
-      </c>
-      <c r="H19" t="s">
-        <v>49</v>
-      </c>
-      <c r="I19" t="s">
-        <v>50</v>
-      </c>
-      <c r="J19" t="s">
-        <v>50</v>
-      </c>
-      <c r="K19" t="s">
-        <v>51</v>
-      </c>
-      <c r="L19" t="s">
-        <v>52</v>
-      </c>
-      <c r="M19" s="5">
-        <v>2</v>
-      </c>
-      <c r="N19" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="O19" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15">
-      <c r="A20" t="s">
-        <v>113</v>
-      </c>
-      <c r="B20" t="s">
-        <v>114</v>
-      </c>
-      <c r="C20" t="s">
-        <v>46</v>
-      </c>
-      <c r="D20" s="2">
-        <v>4</v>
-      </c>
-      <c r="E20" t="s">
-        <v>47</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="G20" t="s">
-        <v>49</v>
-      </c>
-      <c r="H20" t="s">
-        <v>49</v>
-      </c>
-      <c r="I20" t="s">
-        <v>50</v>
-      </c>
-      <c r="J20" t="s">
-        <v>50</v>
-      </c>
-      <c r="K20" t="s">
-        <v>116</v>
-      </c>
-      <c r="L20" t="s">
-        <v>52</v>
-      </c>
-      <c r="M20" s="5">
-        <v>1</v>
-      </c>
-      <c r="N20" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="O20" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="21" ht="14.25" customHeight="1" spans="1:15">
-      <c r="A21" t="s">
-        <v>118</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="C21" t="s">
-        <v>65</v>
-      </c>
-      <c r="D21" s="2">
-        <v>4</v>
-      </c>
-      <c r="E21" t="s">
-        <v>66</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="G21" t="s">
-        <v>67</v>
-      </c>
-      <c r="H21" t="s">
-        <v>49</v>
-      </c>
-      <c r="I21" t="s">
-        <v>68</v>
-      </c>
-      <c r="J21" t="s">
-        <v>53</v>
-      </c>
-      <c r="K21" t="s">
-        <v>49</v>
-      </c>
-      <c r="L21" t="s">
-        <v>61</v>
-      </c>
-      <c r="M21" s="5">
-        <v>2</v>
-      </c>
-      <c r="N21" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="O21" t="s">
-        <v>63</v>
+      <c r="O21" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="P21" t="s">
+        <v>131</v>
       </c>
     </row>
   </sheetData>

--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/制造_职业配置表_Manufacture_ClassConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/制造_职业配置表_Manufacture_ClassConfig.xlsx
@@ -1060,7 +1060,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1070,6 +1070,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1613,16 +1616,16 @@
       <c r="G4" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="5">
         <v>0.35</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="K4" t="s">
+      <c r="K4" s="5" t="s">
         <v>57</v>
       </c>
       <c r="L4">
@@ -1634,10 +1637,10 @@
       <c r="N4" t="s">
         <v>58</v>
       </c>
-      <c r="O4" s="5" t="s">
+      <c r="O4" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="P4" s="6" t="s">
+      <c r="P4" s="7" t="s">
         <v>60</v>
       </c>
     </row>
@@ -1660,16 +1663,16 @@
       <c r="G5" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J5" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="K5" t="s">
+      <c r="K5" s="5" t="s">
         <v>59</v>
       </c>
       <c r="L5">
@@ -1681,10 +1684,10 @@
       <c r="N5" t="s">
         <v>67</v>
       </c>
-      <c r="O5" s="5">
+      <c r="O5" s="6">
         <v>4</v>
       </c>
-      <c r="P5" s="6" t="s">
+      <c r="P5" s="7" t="s">
         <v>68</v>
       </c>
     </row>
@@ -1707,16 +1710,16 @@
       <c r="G6" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H6" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="J6" t="s">
+      <c r="J6" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="K6" t="s">
+      <c r="K6" s="5" t="s">
         <v>59</v>
       </c>
       <c r="L6">
@@ -1728,10 +1731,10 @@
       <c r="N6" t="s">
         <v>67</v>
       </c>
-      <c r="O6" s="5">
+      <c r="O6" s="6">
         <v>3</v>
       </c>
-      <c r="P6" s="6" t="s">
+      <c r="P6" s="7" t="s">
         <v>75</v>
       </c>
     </row>
@@ -1754,16 +1757,16 @@
       <c r="G7" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="5">
         <v>0.35</v>
       </c>
-      <c r="I7" t="s">
+      <c r="I7" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="J7" t="s">
+      <c r="J7" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="K7" t="s">
+      <c r="K7" s="5" t="s">
         <v>57</v>
       </c>
       <c r="L7">
@@ -1775,10 +1778,10 @@
       <c r="N7" t="s">
         <v>58</v>
       </c>
-      <c r="O7" s="5">
+      <c r="O7" s="6">
         <v>2</v>
       </c>
-      <c r="P7" s="6" t="s">
+      <c r="P7" s="7" t="s">
         <v>79</v>
       </c>
     </row>
@@ -1801,16 +1804,16 @@
       <c r="G8" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="H8" t="s">
+      <c r="H8" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="I8" t="s">
+      <c r="I8" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="J8" t="s">
+      <c r="J8" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="K8" t="s">
+      <c r="K8" s="5" t="s">
         <v>57</v>
       </c>
       <c r="L8">
@@ -1822,10 +1825,10 @@
       <c r="N8" t="s">
         <v>58</v>
       </c>
-      <c r="O8" s="5" t="s">
+      <c r="O8" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="P8" s="6" t="s">
+      <c r="P8" s="7" t="s">
         <v>82</v>
       </c>
       <c r="Q8" t="s">
@@ -1851,16 +1854,16 @@
       <c r="G9" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="H9" t="s">
+      <c r="H9" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="I9" t="s">
+      <c r="I9" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="J9" t="s">
+      <c r="J9" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="K9" t="s">
+      <c r="K9" s="5" t="s">
         <v>59</v>
       </c>
       <c r="L9">
@@ -1872,10 +1875,10 @@
       <c r="N9" t="s">
         <v>67</v>
       </c>
-      <c r="O9" s="5">
+      <c r="O9" s="6">
         <v>4</v>
       </c>
-      <c r="P9" s="6" t="s">
+      <c r="P9" s="7" t="s">
         <v>85</v>
       </c>
       <c r="Q9" t="s">
@@ -1901,16 +1904,16 @@
       <c r="G10" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="H10" t="s">
+      <c r="H10" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="I10" t="s">
+      <c r="I10" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="J10" t="s">
+      <c r="J10" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="K10" t="s">
+      <c r="K10" s="5" t="s">
         <v>59</v>
       </c>
       <c r="L10">
@@ -1922,10 +1925,10 @@
       <c r="N10" t="s">
         <v>67</v>
       </c>
-      <c r="O10" s="5">
+      <c r="O10" s="6">
         <v>3</v>
       </c>
-      <c r="P10" s="6" t="s">
+      <c r="P10" s="7" t="s">
         <v>88</v>
       </c>
       <c r="Q10" t="s">
@@ -1954,16 +1957,16 @@
       <c r="G11" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="5">
         <v>0.35</v>
       </c>
-      <c r="I11" t="s">
+      <c r="I11" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="J11" t="s">
+      <c r="J11" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="K11" t="s">
+      <c r="K11" s="5" t="s">
         <v>57</v>
       </c>
       <c r="L11">
@@ -1975,10 +1978,10 @@
       <c r="N11" t="s">
         <v>58</v>
       </c>
-      <c r="O11" s="5">
+      <c r="O11" s="6">
         <v>2</v>
       </c>
-      <c r="P11" s="6" t="s">
+      <c r="P11" s="7" t="s">
         <v>91</v>
       </c>
       <c r="Q11" t="s">
@@ -1989,13 +1992,13 @@
       <c r="A12" t="s">
         <v>93</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="8" t="s">
         <v>94</v>
       </c>
       <c r="C12" t="s">
         <v>53</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="8" t="s">
         <v>94</v>
       </c>
       <c r="E12" s="2">
@@ -2007,16 +2010,16 @@
       <c r="G12" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="5">
         <v>0.35</v>
       </c>
-      <c r="I12" t="s">
+      <c r="I12" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="J12" t="s">
+      <c r="J12" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="K12" t="s">
+      <c r="K12" s="5" t="s">
         <v>57</v>
       </c>
       <c r="L12">
@@ -2028,10 +2031,10 @@
       <c r="N12" t="s">
         <v>58</v>
       </c>
-      <c r="O12" s="5" t="s">
+      <c r="O12" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="P12" s="6" t="s">
+      <c r="P12" s="7" t="s">
         <v>95</v>
       </c>
       <c r="Q12" t="s">
@@ -2042,13 +2045,13 @@
       <c r="A13" t="s">
         <v>97</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="8" t="s">
         <v>98</v>
       </c>
       <c r="C13" t="s">
         <v>63</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="8" t="s">
         <v>98</v>
       </c>
       <c r="E13" s="2">
@@ -2060,16 +2063,16 @@
       <c r="G13" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="H13" t="s">
+      <c r="H13" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="I13" t="s">
+      <c r="I13" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="J13" t="s">
+      <c r="J13" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="K13" t="s">
+      <c r="K13" s="5" t="s">
         <v>59</v>
       </c>
       <c r="L13">
@@ -2081,10 +2084,10 @@
       <c r="N13" t="s">
         <v>67</v>
       </c>
-      <c r="O13" s="5">
+      <c r="O13" s="6">
         <v>4</v>
       </c>
-      <c r="P13" s="6" t="s">
+      <c r="P13" s="7" t="s">
         <v>99</v>
       </c>
       <c r="Q13" t="s">
@@ -2095,13 +2098,13 @@
       <c r="A14" t="s">
         <v>101</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="7" t="s">
         <v>102</v>
       </c>
       <c r="C14" t="s">
         <v>71</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="7" t="s">
         <v>102</v>
       </c>
       <c r="E14" s="2">
@@ -2113,16 +2116,16 @@
       <c r="G14" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="H14" t="s">
+      <c r="H14" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="I14" t="s">
+      <c r="I14" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="J14" t="s">
+      <c r="J14" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="K14" t="s">
+      <c r="K14" s="5" t="s">
         <v>59</v>
       </c>
       <c r="L14">
@@ -2134,10 +2137,10 @@
       <c r="N14" t="s">
         <v>67</v>
       </c>
-      <c r="O14" s="5">
+      <c r="O14" s="6">
         <v>3</v>
       </c>
-      <c r="P14" s="6" t="s">
+      <c r="P14" s="7" t="s">
         <v>103</v>
       </c>
       <c r="Q14" t="s">
@@ -2148,13 +2151,13 @@
       <c r="A15" t="s">
         <v>105</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="7" t="s">
         <v>106</v>
       </c>
       <c r="C15" t="s">
         <v>78</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="7" t="s">
         <v>106</v>
       </c>
       <c r="E15" s="2">
@@ -2166,16 +2169,16 @@
       <c r="G15" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="5">
         <v>0.35</v>
       </c>
-      <c r="I15" t="s">
+      <c r="I15" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="J15" t="s">
+      <c r="J15" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="K15" t="s">
+      <c r="K15" s="5" t="s">
         <v>57</v>
       </c>
       <c r="L15">
@@ -2187,10 +2190,10 @@
       <c r="N15" t="s">
         <v>58</v>
       </c>
-      <c r="O15" s="5">
+      <c r="O15" s="6">
         <v>2</v>
       </c>
-      <c r="P15" s="6" t="s">
+      <c r="P15" s="7" t="s">
         <v>107</v>
       </c>
       <c r="Q15" t="s">
@@ -2219,16 +2222,16 @@
       <c r="G16" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="5">
         <v>0.35</v>
       </c>
-      <c r="I16" t="s">
+      <c r="I16" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="J16" t="s">
+      <c r="J16" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="K16" t="s">
+      <c r="K16" s="5" t="s">
         <v>57</v>
       </c>
       <c r="L16">
@@ -2240,10 +2243,10 @@
       <c r="N16" t="s">
         <v>58</v>
       </c>
-      <c r="O16" s="5" t="s">
+      <c r="O16" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="P16" s="6" t="s">
+      <c r="P16" s="7" t="s">
         <v>111</v>
       </c>
       <c r="Q16" t="s">
@@ -2254,13 +2257,13 @@
       <c r="A17" t="s">
         <v>113</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="7" t="s">
         <v>114</v>
       </c>
       <c r="C17" t="s">
         <v>63</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D17" s="7" t="s">
         <v>114</v>
       </c>
       <c r="E17" s="2">
@@ -2272,16 +2275,16 @@
       <c r="G17" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="H17" t="s">
+      <c r="H17" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="I17" t="s">
+      <c r="I17" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="J17" t="s">
+      <c r="J17" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="K17" t="s">
+      <c r="K17" s="5" t="s">
         <v>59</v>
       </c>
       <c r="L17">
@@ -2293,10 +2296,10 @@
       <c r="N17" t="s">
         <v>67</v>
       </c>
-      <c r="O17" s="5">
+      <c r="O17" s="6">
         <v>4</v>
       </c>
-      <c r="P17" s="6" t="s">
+      <c r="P17" s="7" t="s">
         <v>115</v>
       </c>
       <c r="Q17" t="s">
@@ -2307,13 +2310,13 @@
       <c r="A18" t="s">
         <v>117</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="7" t="s">
         <v>118</v>
       </c>
       <c r="C18" t="s">
         <v>71</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="7" t="s">
         <v>118</v>
       </c>
       <c r="E18" s="2">
@@ -2325,16 +2328,16 @@
       <c r="G18" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="H18" t="s">
+      <c r="H18" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="I18" t="s">
+      <c r="I18" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="J18" t="s">
+      <c r="J18" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="K18" t="s">
+      <c r="K18" s="5" t="s">
         <v>59</v>
       </c>
       <c r="L18">
@@ -2346,10 +2349,10 @@
       <c r="N18" t="s">
         <v>67</v>
       </c>
-      <c r="O18" s="5">
+      <c r="O18" s="6">
         <v>3</v>
       </c>
-      <c r="P18" s="6" t="s">
+      <c r="P18" s="7" t="s">
         <v>119</v>
       </c>
       <c r="Q18" t="s">
@@ -2360,13 +2363,13 @@
       <c r="A19" t="s">
         <v>121</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="7" t="s">
         <v>122</v>
       </c>
       <c r="C19" t="s">
         <v>78</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="D19" s="7" t="s">
         <v>122</v>
       </c>
       <c r="E19" s="2">
@@ -2378,16 +2381,16 @@
       <c r="G19" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="5">
         <v>0.35</v>
       </c>
-      <c r="I19" t="s">
+      <c r="I19" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="J19" t="s">
+      <c r="J19" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="K19" t="s">
+      <c r="K19" s="5" t="s">
         <v>57</v>
       </c>
       <c r="L19">
@@ -2399,10 +2402,10 @@
       <c r="N19" t="s">
         <v>58</v>
       </c>
-      <c r="O19" s="5">
+      <c r="O19" s="6">
         <v>2</v>
       </c>
-      <c r="P19" s="6" t="s">
+      <c r="P19" s="7" t="s">
         <v>123</v>
       </c>
       <c r="Q19" t="s">
@@ -2431,16 +2434,16 @@
       <c r="G20" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="H20" t="s">
+      <c r="H20" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="I20" t="s">
+      <c r="I20" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="J20" t="s">
+      <c r="J20" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="K20" t="s">
+      <c r="K20" s="5" t="s">
         <v>57</v>
       </c>
       <c r="L20">
@@ -2452,10 +2455,10 @@
       <c r="N20" t="s">
         <v>58</v>
       </c>
-      <c r="O20" s="5">
+      <c r="O20" s="6">
         <v>1</v>
       </c>
-      <c r="P20" s="7" t="s">
+      <c r="P20" s="8" t="s">
         <v>127</v>
       </c>
       <c r="Q20" t="s">
@@ -2466,13 +2469,13 @@
       <c r="A21" t="s">
         <v>129</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="7" t="s">
         <v>130</v>
       </c>
       <c r="C21" t="s">
         <v>71</v>
       </c>
-      <c r="D21" s="6" t="s">
+      <c r="D21" s="7" t="s">
         <v>130</v>
       </c>
       <c r="E21" s="2">
@@ -2484,16 +2487,16 @@
       <c r="G21" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="H21" t="s">
+      <c r="H21" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="I21" t="s">
+      <c r="I21" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="J21" t="s">
+      <c r="J21" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="K21" t="s">
+      <c r="K21" s="5" t="s">
         <v>59</v>
       </c>
       <c r="L21">
@@ -2505,10 +2508,10 @@
       <c r="N21" t="s">
         <v>67</v>
       </c>
-      <c r="O21" s="5">
+      <c r="O21" s="6">
         <v>2</v>
       </c>
-      <c r="P21" s="7" t="s">
+      <c r="P21" s="8" t="s">
         <v>131</v>
       </c>
       <c r="Q21" t="s">

--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/制造_职业配置表_Manufacture_ClassConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/制造_职业配置表_Manufacture_ClassConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="139">
   <si>
     <t>职业ID</t>
   </si>
@@ -85,6 +85,9 @@
     <t>制造默认获得技能ID</t>
   </si>
   <si>
+    <t>士兵简画图标</t>
+  </si>
+  <si>
     <t>主键；被 SoulConfig.ClassId 引用</t>
   </si>
   <si>
@@ -136,6 +139,9 @@
     <t>空=无；SkillId 或 SkillId|SkillId；FK → SkillConfig.SkillId</t>
   </si>
   <si>
+    <t>UI-033 战斗指示器简画；仅文件名；Resources/UI/Icons/{Id}；空=空框</t>
+  </si>
+  <si>
     <t>ClassId</t>
   </si>
   <si>
@@ -187,6 +193,9 @@
     <t>DefaultSkillIds</t>
   </si>
   <si>
+    <t>SilhouetteIconAssetId</t>
+  </si>
+  <si>
     <t>Class_BaseWarrior</t>
   </si>
   <si>
@@ -217,6 +226,9 @@
     <t>App_0_00</t>
   </si>
   <si>
+    <t>HPPK_UI_Class_BaseWarrior</t>
+  </si>
+  <si>
     <t>Class_BaseArcher</t>
   </si>
   <si>
@@ -241,6 +253,9 @@
     <t>App_0_10</t>
   </si>
   <si>
+    <t>HPPK_UI_Class_BaseArcher</t>
+  </si>
+  <si>
     <t>Class_BaseMage</t>
   </si>
   <si>
@@ -262,6 +277,9 @@
     <t>App_0_20</t>
   </si>
   <si>
+    <t>HPPK_UI_Class_BaseMage</t>
+  </si>
+  <si>
     <t>Class_BaseRogue</t>
   </si>
   <si>
@@ -272,6 +290,9 @@
   </si>
   <si>
     <t>App_0_30</t>
+  </si>
+  <si>
+    <t>HPPK_UI_Class_BaseRogue</t>
   </si>
   <si>
     <t>Class_Warrior</t>
@@ -1060,7 +1081,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1070,9 +1091,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1426,7 +1444,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:R21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -1438,7 +1456,7 @@
     <col min="13" max="13" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:18">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1490,143 +1508,152 @@
       <c r="Q1" t="s">
         <v>16</v>
       </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:18">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q2" t="s">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R2" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:17">
+    <row r="3" s="1" customFormat="1" spans="1:18">
       <c r="A3" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
+      </c>
+      <c r="R3" t="s">
+        <v>53</v>
       </c>
     </row>
-    <row r="4" ht="14.25" customHeight="1" spans="1:17">
+    <row r="4" ht="14.25" customHeight="1" spans="1:18">
       <c r="A4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B4" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E4" s="2">
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="H4" s="5">
+        <v>58</v>
+      </c>
+      <c r="H4" s="2">
         <v>0.35</v>
       </c>
-      <c r="I4" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>57</v>
+      <c r="I4" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>60</v>
       </c>
       <c r="L4">
         <v>1.2</v>
@@ -1635,45 +1662,48 @@
         <v>1.1</v>
       </c>
       <c r="N4" t="s">
-        <v>58</v>
-      </c>
-      <c r="O4" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="P4" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="O4" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="P4" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="R4" t="s">
+        <v>64</v>
       </c>
     </row>
-    <row r="5" ht="14.25" customHeight="1" spans="1:17">
+    <row r="5" ht="14.25" customHeight="1" spans="1:18">
       <c r="A5" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B5" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E5" s="2">
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="H5" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="I5" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>59</v>
+      <c r="J5" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="L5">
         <v>1.2</v>
@@ -1682,45 +1712,48 @@
         <v>1</v>
       </c>
       <c r="N5" t="s">
-        <v>67</v>
-      </c>
-      <c r="O5" s="6">
+        <v>71</v>
+      </c>
+      <c r="O5" s="5">
         <v>4</v>
       </c>
-      <c r="P5" s="7" t="s">
-        <v>68</v>
+      <c r="P5" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="R5" t="s">
+        <v>73</v>
       </c>
     </row>
-    <row r="6" ht="14.25" customHeight="1" spans="1:17">
+    <row r="6" ht="14.25" customHeight="1" spans="1:18">
       <c r="A6" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="E6" s="2">
         <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="K6" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>59</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="L6">
         <v>1.2</v>
@@ -1729,45 +1762,48 @@
         <v>1</v>
       </c>
       <c r="N6" t="s">
-        <v>67</v>
-      </c>
-      <c r="O6" s="6">
+        <v>71</v>
+      </c>
+      <c r="O6" s="5">
         <v>3</v>
       </c>
-      <c r="P6" s="7" t="s">
-        <v>75</v>
+      <c r="P6" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="R6" t="s">
+        <v>81</v>
       </c>
     </row>
-    <row r="7" ht="14.25" customHeight="1" spans="1:17">
+    <row r="7" ht="14.25" customHeight="1" spans="1:18">
       <c r="A7" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C7" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="E7" s="2">
         <v>1</v>
       </c>
       <c r="F7" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="H7" s="5">
+        <v>69</v>
+      </c>
+      <c r="H7" s="2">
         <v>0.35</v>
       </c>
-      <c r="I7" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="K7" s="5" t="s">
-        <v>57</v>
+      <c r="I7" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>60</v>
       </c>
       <c r="L7">
         <v>1.2</v>
@@ -1776,45 +1812,48 @@
         <v>1.15</v>
       </c>
       <c r="N7" t="s">
-        <v>58</v>
-      </c>
-      <c r="O7" s="6">
+        <v>61</v>
+      </c>
+      <c r="O7" s="5">
         <v>2</v>
       </c>
-      <c r="P7" s="7" t="s">
-        <v>79</v>
+      <c r="P7" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="R7" t="s">
+        <v>86</v>
       </c>
     </row>
-    <row r="8" ht="14.25" customHeight="1" spans="1:17">
+    <row r="8" ht="14.25" customHeight="1" spans="1:18">
       <c r="A8" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="B8" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C8" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E8" s="2">
         <v>2</v>
       </c>
       <c r="F8" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="K8" s="5" t="s">
-        <v>57</v>
+        <v>69</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>60</v>
       </c>
       <c r="L8">
         <v>1.2</v>
@@ -1823,48 +1862,51 @@
         <v>1.1</v>
       </c>
       <c r="N8" t="s">
-        <v>58</v>
-      </c>
-      <c r="O8" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="P8" s="7" t="s">
-        <v>82</v>
+        <v>61</v>
+      </c>
+      <c r="O8" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="P8" s="6" t="s">
+        <v>89</v>
       </c>
       <c r="Q8" t="s">
-        <v>83</v>
+        <v>90</v>
+      </c>
+      <c r="R8" t="s">
+        <v>64</v>
       </c>
     </row>
-    <row r="9" ht="14.25" customHeight="1" spans="1:17">
+    <row r="9" ht="14.25" customHeight="1" spans="1:18">
       <c r="A9" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="B9" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C9" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E9" s="2">
         <v>2</v>
       </c>
       <c r="F9" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="H9" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="I9" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="J9" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="K9" s="5" t="s">
-        <v>59</v>
+      <c r="J9" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="L9">
         <v>1.2</v>
@@ -1873,48 +1915,51 @@
         <v>1</v>
       </c>
       <c r="N9" t="s">
-        <v>67</v>
-      </c>
-      <c r="O9" s="6">
+        <v>71</v>
+      </c>
+      <c r="O9" s="5">
         <v>4</v>
       </c>
-      <c r="P9" s="7" t="s">
-        <v>85</v>
+      <c r="P9" s="6" t="s">
+        <v>92</v>
       </c>
       <c r="Q9" t="s">
-        <v>86</v>
+        <v>93</v>
+      </c>
+      <c r="R9" t="s">
+        <v>73</v>
       </c>
     </row>
-    <row r="10" ht="14.25" customHeight="1" spans="1:17">
+    <row r="10" ht="14.25" customHeight="1" spans="1:18">
       <c r="A10" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C10" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="E10" s="2">
         <v>2</v>
       </c>
       <c r="F10" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="I10" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="J10" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="K10" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>59</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="L10">
         <v>1.2</v>
@@ -1923,51 +1968,54 @@
         <v>1</v>
       </c>
       <c r="N10" t="s">
-        <v>67</v>
-      </c>
-      <c r="O10" s="6">
+        <v>71</v>
+      </c>
+      <c r="O10" s="5">
         <v>3</v>
       </c>
-      <c r="P10" s="7" t="s">
-        <v>88</v>
+      <c r="P10" s="6" t="s">
+        <v>95</v>
       </c>
       <c r="Q10" t="s">
-        <v>89</v>
+        <v>96</v>
+      </c>
+      <c r="R10" t="s">
+        <v>81</v>
       </c>
     </row>
-    <row r="11" ht="14.25" customHeight="1" spans="1:17">
+    <row r="11" ht="14.25" customHeight="1" spans="1:18">
       <c r="A11" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="B11" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C11" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="D11" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="E11" s="2">
         <v>2</v>
       </c>
       <c r="F11" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="H11" s="5">
+        <v>69</v>
+      </c>
+      <c r="H11" s="2">
         <v>0.35</v>
       </c>
-      <c r="I11" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="J11" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="K11" s="5" t="s">
-        <v>57</v>
+      <c r="I11" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>60</v>
       </c>
       <c r="L11">
         <v>1.2</v>
@@ -1976,51 +2024,54 @@
         <v>1.15</v>
       </c>
       <c r="N11" t="s">
-        <v>58</v>
-      </c>
-      <c r="O11" s="6">
+        <v>61</v>
+      </c>
+      <c r="O11" s="5">
         <v>2</v>
       </c>
-      <c r="P11" s="7" t="s">
-        <v>91</v>
+      <c r="P11" s="6" t="s">
+        <v>98</v>
       </c>
       <c r="Q11" t="s">
-        <v>92</v>
+        <v>99</v>
+      </c>
+      <c r="R11" t="s">
+        <v>86</v>
       </c>
     </row>
-    <row r="12" ht="14.25" customHeight="1" spans="1:17">
+    <row r="12" ht="14.25" customHeight="1" spans="1:18">
       <c r="A12" t="s">
-        <v>93</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>94</v>
+        <v>100</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>101</v>
       </c>
       <c r="C12" t="s">
-        <v>53</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>94</v>
+        <v>56</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>101</v>
       </c>
       <c r="E12" s="2">
         <v>3</v>
       </c>
       <c r="F12" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="H12" s="5">
+        <v>69</v>
+      </c>
+      <c r="H12" s="2">
         <v>0.35</v>
       </c>
-      <c r="I12" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="J12" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="K12" s="5" t="s">
-        <v>57</v>
+      <c r="I12" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>60</v>
       </c>
       <c r="L12">
         <v>1.2</v>
@@ -2029,51 +2080,54 @@
         <v>1</v>
       </c>
       <c r="N12" t="s">
-        <v>58</v>
-      </c>
-      <c r="O12" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="P12" s="7" t="s">
-        <v>95</v>
+        <v>61</v>
+      </c>
+      <c r="O12" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="P12" s="6" t="s">
+        <v>102</v>
       </c>
       <c r="Q12" t="s">
-        <v>96</v>
+        <v>103</v>
+      </c>
+      <c r="R12" t="s">
+        <v>64</v>
       </c>
     </row>
-    <row r="13" ht="14.25" customHeight="1" spans="1:17">
+    <row r="13" ht="14.25" customHeight="1" spans="1:18">
       <c r="A13" t="s">
-        <v>97</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>98</v>
+        <v>104</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>105</v>
       </c>
       <c r="C13" t="s">
-        <v>63</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>98</v>
+        <v>67</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>105</v>
       </c>
       <c r="E13" s="2">
         <v>3</v>
       </c>
       <c r="F13" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="H13" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="I13" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="J13" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="K13" s="5" t="s">
-        <v>59</v>
+      <c r="J13" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="L13">
         <v>1.2</v>
@@ -2082,51 +2136,54 @@
         <v>1</v>
       </c>
       <c r="N13" t="s">
-        <v>67</v>
-      </c>
-      <c r="O13" s="6">
+        <v>71</v>
+      </c>
+      <c r="O13" s="5">
         <v>4</v>
       </c>
-      <c r="P13" s="7" t="s">
-        <v>99</v>
+      <c r="P13" s="6" t="s">
+        <v>106</v>
       </c>
       <c r="Q13" t="s">
-        <v>100</v>
+        <v>107</v>
+      </c>
+      <c r="R13" t="s">
+        <v>73</v>
       </c>
     </row>
-    <row r="14" ht="14.25" customHeight="1" spans="1:17">
+    <row r="14" ht="14.25" customHeight="1" spans="1:18">
       <c r="A14" t="s">
-        <v>101</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>102</v>
+        <v>108</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>109</v>
       </c>
       <c r="C14" t="s">
-        <v>71</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>102</v>
+        <v>76</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>109</v>
       </c>
       <c r="E14" s="2">
         <v>3</v>
       </c>
       <c r="F14" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="I14" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="J14" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="K14" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>59</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="L14">
         <v>1.2</v>
@@ -2135,51 +2192,54 @@
         <v>1</v>
       </c>
       <c r="N14" t="s">
-        <v>67</v>
-      </c>
-      <c r="O14" s="6">
+        <v>71</v>
+      </c>
+      <c r="O14" s="5">
         <v>3</v>
       </c>
-      <c r="P14" s="7" t="s">
-        <v>103</v>
+      <c r="P14" s="6" t="s">
+        <v>110</v>
       </c>
       <c r="Q14" t="s">
-        <v>104</v>
+        <v>111</v>
+      </c>
+      <c r="R14" t="s">
+        <v>81</v>
       </c>
     </row>
-    <row r="15" ht="14.25" customHeight="1" spans="1:17">
+    <row r="15" ht="14.25" customHeight="1" spans="1:18">
       <c r="A15" t="s">
-        <v>105</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>106</v>
+        <v>112</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>113</v>
       </c>
       <c r="C15" t="s">
-        <v>78</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>106</v>
+        <v>84</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>113</v>
       </c>
       <c r="E15" s="2">
         <v>3</v>
       </c>
       <c r="F15" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="H15" s="5">
+        <v>69</v>
+      </c>
+      <c r="H15" s="2">
         <v>0.35</v>
       </c>
-      <c r="I15" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="J15" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="K15" s="5" t="s">
-        <v>57</v>
+      <c r="I15" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>60</v>
       </c>
       <c r="L15">
         <v>1.2</v>
@@ -2188,51 +2248,54 @@
         <v>1.15</v>
       </c>
       <c r="N15" t="s">
-        <v>58</v>
-      </c>
-      <c r="O15" s="6">
+        <v>61</v>
+      </c>
+      <c r="O15" s="5">
         <v>2</v>
       </c>
-      <c r="P15" s="7" t="s">
-        <v>107</v>
+      <c r="P15" s="6" t="s">
+        <v>114</v>
       </c>
       <c r="Q15" t="s">
-        <v>108</v>
+        <v>115</v>
+      </c>
+      <c r="R15" t="s">
+        <v>86</v>
       </c>
     </row>
-    <row r="16" ht="14.25" customHeight="1" spans="1:17">
+    <row r="16" ht="14.25" customHeight="1" spans="1:18">
       <c r="A16" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="B16" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="C16" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D16" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="E16" s="2">
         <v>3</v>
       </c>
       <c r="F16" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="H16" s="5">
+        <v>69</v>
+      </c>
+      <c r="H16" s="2">
         <v>0.35</v>
       </c>
-      <c r="I16" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="J16" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="K16" s="5" t="s">
-        <v>57</v>
+      <c r="I16" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>60</v>
       </c>
       <c r="L16">
         <v>1.2</v>
@@ -2241,51 +2304,54 @@
         <v>1.1</v>
       </c>
       <c r="N16" t="s">
-        <v>58</v>
-      </c>
-      <c r="O16" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="P16" s="7" t="s">
-        <v>111</v>
+        <v>61</v>
+      </c>
+      <c r="O16" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="P16" s="6" t="s">
+        <v>118</v>
       </c>
       <c r="Q16" t="s">
-        <v>112</v>
+        <v>119</v>
+      </c>
+      <c r="R16" t="s">
+        <v>64</v>
       </c>
     </row>
-    <row r="17" ht="14.25" customHeight="1" spans="1:17">
+    <row r="17" ht="14.25" customHeight="1" spans="1:18">
       <c r="A17" t="s">
-        <v>113</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>114</v>
+        <v>120</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>121</v>
       </c>
       <c r="C17" t="s">
-        <v>63</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>114</v>
+        <v>67</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>121</v>
       </c>
       <c r="E17" s="2">
         <v>3</v>
       </c>
       <c r="F17" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="H17" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="I17" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="J17" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="K17" s="5" t="s">
-        <v>59</v>
+      <c r="J17" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="L17">
         <v>1.2</v>
@@ -2294,51 +2360,54 @@
         <v>1</v>
       </c>
       <c r="N17" t="s">
-        <v>67</v>
-      </c>
-      <c r="O17" s="6">
+        <v>71</v>
+      </c>
+      <c r="O17" s="5">
         <v>4</v>
       </c>
-      <c r="P17" s="7" t="s">
-        <v>115</v>
+      <c r="P17" s="6" t="s">
+        <v>122</v>
       </c>
       <c r="Q17" t="s">
-        <v>116</v>
+        <v>123</v>
+      </c>
+      <c r="R17" t="s">
+        <v>73</v>
       </c>
     </row>
-    <row r="18" ht="14.25" customHeight="1" spans="1:17">
+    <row r="18" ht="14.25" customHeight="1" spans="1:18">
       <c r="A18" t="s">
-        <v>117</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>118</v>
+        <v>124</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>125</v>
       </c>
       <c r="C18" t="s">
-        <v>71</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>118</v>
+        <v>76</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>125</v>
       </c>
       <c r="E18" s="2">
         <v>3</v>
       </c>
       <c r="F18" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="H18" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="I18" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="J18" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="K18" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>59</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="L18">
         <v>1.2</v>
@@ -2347,51 +2416,54 @@
         <v>1</v>
       </c>
       <c r="N18" t="s">
-        <v>67</v>
-      </c>
-      <c r="O18" s="6">
+        <v>71</v>
+      </c>
+      <c r="O18" s="5">
         <v>3</v>
       </c>
-      <c r="P18" s="7" t="s">
-        <v>119</v>
+      <c r="P18" s="6" t="s">
+        <v>126</v>
       </c>
       <c r="Q18" t="s">
-        <v>120</v>
+        <v>127</v>
+      </c>
+      <c r="R18" t="s">
+        <v>81</v>
       </c>
     </row>
-    <row r="19" ht="14.25" customHeight="1" spans="1:17">
+    <row r="19" ht="14.25" customHeight="1" spans="1:18">
       <c r="A19" t="s">
-        <v>121</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>122</v>
+        <v>128</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>129</v>
       </c>
       <c r="C19" t="s">
-        <v>78</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>122</v>
+        <v>84</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>129</v>
       </c>
       <c r="E19" s="2">
         <v>3</v>
       </c>
       <c r="F19" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="H19" s="5">
+        <v>69</v>
+      </c>
+      <c r="H19" s="2">
         <v>0.35</v>
       </c>
-      <c r="I19" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="J19" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="K19" s="5" t="s">
-        <v>57</v>
+      <c r="I19" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>60</v>
       </c>
       <c r="L19">
         <v>1.2</v>
@@ -2400,51 +2472,54 @@
         <v>1.15</v>
       </c>
       <c r="N19" t="s">
-        <v>58</v>
-      </c>
-      <c r="O19" s="6">
+        <v>61</v>
+      </c>
+      <c r="O19" s="5">
         <v>2</v>
       </c>
-      <c r="P19" s="7" t="s">
-        <v>123</v>
+      <c r="P19" s="6" t="s">
+        <v>130</v>
       </c>
       <c r="Q19" t="s">
-        <v>124</v>
+        <v>131</v>
+      </c>
+      <c r="R19" t="s">
+        <v>86</v>
       </c>
     </row>
-    <row r="20" spans="1:17">
+    <row r="20" spans="1:18">
       <c r="A20" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="B20" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="C20" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D20" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="E20" s="2">
         <v>4</v>
       </c>
       <c r="F20" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="H20" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="I20" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="J20" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="K20" s="5" t="s">
-        <v>57</v>
+        <v>69</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>60</v>
       </c>
       <c r="L20">
         <v>1.2</v>
@@ -2453,51 +2528,54 @@
         <v>1</v>
       </c>
       <c r="N20" t="s">
-        <v>58</v>
-      </c>
-      <c r="O20" s="6">
+        <v>61</v>
+      </c>
+      <c r="O20" s="5">
         <v>1</v>
       </c>
-      <c r="P20" s="8" t="s">
-        <v>127</v>
+      <c r="P20" s="7" t="s">
+        <v>134</v>
       </c>
       <c r="Q20" t="s">
-        <v>128</v>
+        <v>135</v>
+      </c>
+      <c r="R20" t="s">
+        <v>64</v>
       </c>
     </row>
-    <row r="21" ht="14.25" customHeight="1" spans="1:17">
+    <row r="21" ht="14.25" customHeight="1" spans="1:18">
       <c r="A21" t="s">
-        <v>129</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>130</v>
+        <v>136</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>137</v>
       </c>
       <c r="C21" t="s">
-        <v>71</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>130</v>
+        <v>76</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>137</v>
       </c>
       <c r="E21" s="2">
         <v>4</v>
       </c>
       <c r="F21" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="H21" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="I21" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="J21" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="K21" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>59</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="L21">
         <v>1.2</v>
@@ -2506,16 +2584,19 @@
         <v>1</v>
       </c>
       <c r="N21" t="s">
-        <v>67</v>
-      </c>
-      <c r="O21" s="6">
+        <v>71</v>
+      </c>
+      <c r="O21" s="5">
         <v>2</v>
       </c>
-      <c r="P21" s="8" t="s">
-        <v>131</v>
+      <c r="P21" s="7" t="s">
+        <v>138</v>
       </c>
       <c r="Q21" t="s">
-        <v>128</v>
+        <v>135</v>
+      </c>
+      <c r="R21" t="s">
+        <v>81</v>
       </c>
     </row>
   </sheetData>
